--- a/Data/output/reforms/output/reform_panel.xlsx
+++ b/Data/output/reforms/output/reform_panel.xlsx
@@ -28665,16 +28665,16 @@
         <v>1997</v>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -28689,16 +28689,16 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P314" t="n">
         <v>0</v>
@@ -28722,7 +28722,7 @@
         <v>0</v>
       </c>
       <c r="W314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X314" t="n">
         <v>0</v>
@@ -28731,13 +28731,13 @@
         <v>0</v>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB314" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="315">
@@ -28893,7 +28893,7 @@
         <v>0</v>
       </c>
       <c r="T316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U316" t="n">
         <v>0</v>
@@ -29115,16 +29115,16 @@
         <v>2002</v>
       </c>
       <c r="D319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -29139,16 +29139,16 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -29169,7 +29169,7 @@
         <v>0</v>
       </c>
       <c r="V319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W319" t="n">
         <v>0</v>
@@ -29178,16 +29178,16 @@
         <v>0</v>
       </c>
       <c r="Y319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z319" t="n">
         <v>0</v>
       </c>
       <c r="AA319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB319" t="n">
-        <v>0</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="320">
@@ -29295,40 +29295,40 @@
         <v>2004</v>
       </c>
       <c r="D321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P321" t="n">
         <v>0</v>
@@ -29352,7 +29352,7 @@
         <v>0</v>
       </c>
       <c r="W321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X321" t="n">
         <v>0</v>
@@ -29361,13 +29361,13 @@
         <v>0</v>
       </c>
       <c r="Z321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA321" t="n">
         <v>0</v>
       </c>
       <c r="AB321" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="322">
@@ -29385,16 +29385,16 @@
         <v>2005</v>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -29409,16 +29409,16 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P322" t="n">
         <v>0</v>
@@ -29442,13 +29442,13 @@
         <v>0</v>
       </c>
       <c r="W322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X322" t="n">
         <v>0</v>
       </c>
       <c r="Y322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z322" t="n">
         <v>0</v>
@@ -29457,7 +29457,7 @@
         <v>0</v>
       </c>
       <c r="AB322" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="323">
@@ -29565,40 +29565,40 @@
         <v>2007</v>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P324" t="n">
         <v>0</v>
@@ -29616,19 +29616,19 @@
         <v>0</v>
       </c>
       <c r="U324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V324" t="n">
         <v>0</v>
       </c>
       <c r="W324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X324" t="n">
         <v>0</v>
       </c>
       <c r="Y324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z324" t="n">
         <v>0</v>
@@ -29637,7 +29637,7 @@
         <v>0</v>
       </c>
       <c r="AB324" t="n">
-        <v>0</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="325">
@@ -29745,40 +29745,40 @@
         <v>2009</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P326" t="n">
         <v>0</v>
@@ -29796,10 +29796,10 @@
         <v>0</v>
       </c>
       <c r="U326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W326" t="n">
         <v>0</v>
@@ -29814,10 +29814,10 @@
         <v>0</v>
       </c>
       <c r="AA326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB326" t="n">
-        <v>0</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="327">
@@ -30015,40 +30015,40 @@
         <v>2012</v>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P329" t="n">
         <v>0</v>
@@ -30069,7 +30069,7 @@
         <v>0</v>
       </c>
       <c r="V329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W329" t="n">
         <v>0</v>
@@ -30078,7 +30078,7 @@
         <v>0</v>
       </c>
       <c r="Y329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z329" t="n">
         <v>0</v>
@@ -30087,7 +30087,7 @@
         <v>0</v>
       </c>
       <c r="AB329" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="330">
@@ -30105,40 +30105,40 @@
         <v>2013</v>
       </c>
       <c r="D330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P330" t="n">
         <v>0</v>
@@ -30153,31 +30153,31 @@
         <v>0</v>
       </c>
       <c r="T330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V330" t="n">
         <v>0</v>
       </c>
       <c r="W330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X330" t="n">
         <v>0</v>
       </c>
       <c r="Y330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z330" t="n">
         <v>0</v>
       </c>
       <c r="AA330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB330" t="n">
-        <v>0</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="331">
@@ -30195,40 +30195,40 @@
         <v>2014</v>
       </c>
       <c r="D331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -30246,7 +30246,7 @@
         <v>0</v>
       </c>
       <c r="U331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V331" t="n">
         <v>0</v>
@@ -30255,7 +30255,7 @@
         <v>0</v>
       </c>
       <c r="X331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y331" t="n">
         <v>0</v>
@@ -30267,7 +30267,7 @@
         <v>0</v>
       </c>
       <c r="AB331" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="332">
@@ -30465,16 +30465,16 @@
         <v>2017</v>
       </c>
       <c r="D334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -30489,16 +30489,16 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P334" t="n">
         <v>0</v>
@@ -30522,7 +30522,7 @@
         <v>0</v>
       </c>
       <c r="W334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X334" t="n">
         <v>0</v>
@@ -30537,7 +30537,7 @@
         <v>0</v>
       </c>
       <c r="AB334" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="335">
@@ -30555,40 +30555,40 @@
         <v>2018</v>
       </c>
       <c r="D335" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F335" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N335" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P335" t="n">
         <v>0</v>
@@ -30609,25 +30609,25 @@
         <v>0</v>
       </c>
       <c r="V335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W335" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X335" t="n">
         <v>0</v>
       </c>
       <c r="Y335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z335" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB335" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
     </row>
     <row r="336">
@@ -30645,40 +30645,40 @@
         <v>2019</v>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P336" t="n">
         <v>0</v>
@@ -30693,13 +30693,13 @@
         <v>0</v>
       </c>
       <c r="T336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W336" t="n">
         <v>0</v>
@@ -30708,7 +30708,7 @@
         <v>0</v>
       </c>
       <c r="Y336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z336" t="n">
         <v>0</v>
@@ -30717,7 +30717,7 @@
         <v>0</v>
       </c>
       <c r="AB336" t="n">
-        <v>0</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="337">
@@ -30735,40 +30735,40 @@
         <v>2020</v>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P337" t="n">
         <v>0</v>
@@ -30789,16 +30789,16 @@
         <v>0</v>
       </c>
       <c r="V337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X337" t="n">
         <v>0</v>
       </c>
       <c r="Y337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z337" t="n">
         <v>0</v>
@@ -30807,7 +30807,7 @@
         <v>0</v>
       </c>
       <c r="AB337" t="n">
-        <v>0.552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -30915,16 +30915,16 @@
         <v>2022</v>
       </c>
       <c r="D339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -30939,16 +30939,16 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P339" t="n">
         <v>0</v>
@@ -30966,7 +30966,7 @@
         <v>0</v>
       </c>
       <c r="U339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V339" t="n">
         <v>0</v>
@@ -30978,7 +30978,7 @@
         <v>0</v>
       </c>
       <c r="Y339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z339" t="n">
         <v>0</v>
@@ -30987,7 +30987,7 @@
         <v>0</v>
       </c>
       <c r="AB339" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="340">
@@ -31095,16 +31095,16 @@
         <v>2024</v>
       </c>
       <c r="D341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -31119,16 +31119,16 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P341" t="n">
         <v>0</v>
@@ -31143,31 +31143,31 @@
         <v>0</v>
       </c>
       <c r="T341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U341" t="n">
         <v>0</v>
       </c>
       <c r="V341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X341" t="n">
         <v>0</v>
       </c>
       <c r="Y341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA341" t="n">
         <v>0</v>
       </c>
       <c r="AB341" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="342">
@@ -31233,7 +31233,7 @@
         <v>0</v>
       </c>
       <c r="T342" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U342" t="n">
         <v>0</v>

--- a/Data/output/reforms/output/reform_panel.xlsx
+++ b/Data/output/reforms/output/reform_panel.xlsx
@@ -29475,40 +29475,40 @@
         <v>2006</v>
       </c>
       <c r="D323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P323" t="n">
         <v>0</v>
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="U323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V323" t="n">
         <v>0</v>
@@ -29544,10 +29544,10 @@
         <v>0</v>
       </c>
       <c r="AA323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB323" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="324">
@@ -29565,13 +29565,13 @@
         <v>2007</v>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E324" t="n">
         <v>1</v>
       </c>
       <c r="F324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G324" t="n">
         <v>1</v>
@@ -29589,13 +29589,13 @@
         <v>1</v>
       </c>
       <c r="L324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M324" t="n">
         <v>1</v>
       </c>
       <c r="N324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O324" t="n">
         <v>1</v>
@@ -29622,7 +29622,7 @@
         <v>0</v>
       </c>
       <c r="W324" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X324" t="n">
         <v>0</v>
@@ -29637,7 +29637,7 @@
         <v>0</v>
       </c>
       <c r="AB324" t="n">
-        <v>0.5716</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="325">
@@ -29655,16 +29655,16 @@
         <v>2008</v>
       </c>
       <c r="D325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -29679,16 +29679,16 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P325" t="n">
         <v>0</v>
@@ -29706,16 +29706,16 @@
         <v>0</v>
       </c>
       <c r="U325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W325" t="n">
         <v>0</v>
       </c>
       <c r="X325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y325" t="n">
         <v>0</v>
@@ -29724,10 +29724,10 @@
         <v>0</v>
       </c>
       <c r="AA325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB325" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="326">
@@ -29745,37 +29745,37 @@
         <v>2009</v>
       </c>
       <c r="D326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E326" t="n">
         <v>1</v>
       </c>
       <c r="F326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G326" t="n">
         <v>1</v>
       </c>
       <c r="H326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I326" t="n">
         <v>1</v>
       </c>
       <c r="J326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K326" t="n">
         <v>1</v>
       </c>
       <c r="L326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M326" t="n">
         <v>1</v>
       </c>
       <c r="N326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O326" t="n">
         <v>1</v>
@@ -29796,7 +29796,7 @@
         <v>0</v>
       </c>
       <c r="U326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V326" t="n">
         <v>1</v>
@@ -29814,10 +29814,10 @@
         <v>0</v>
       </c>
       <c r="AA326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB326" t="n">
-        <v>0.707</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="327">
@@ -29835,16 +29835,16 @@
         <v>2010</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -29859,16 +29859,16 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P327" t="n">
         <v>0</v>
@@ -29889,7 +29889,7 @@
         <v>0</v>
       </c>
       <c r="V327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W327" t="n">
         <v>0</v>
@@ -29907,7 +29907,7 @@
         <v>0</v>
       </c>
       <c r="AB327" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="328">
@@ -30015,37 +30015,37 @@
         <v>2012</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E329" t="n">
         <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G329" t="n">
         <v>1</v>
       </c>
       <c r="H329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I329" t="n">
         <v>1</v>
       </c>
       <c r="J329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K329" t="n">
         <v>1</v>
       </c>
       <c r="L329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M329" t="n">
         <v>1</v>
       </c>
       <c r="N329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O329" t="n">
         <v>1</v>
@@ -30066,28 +30066,28 @@
         <v>0</v>
       </c>
       <c r="U329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V329" t="n">
         <v>1</v>
       </c>
       <c r="W329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X329" t="n">
         <v>0</v>
       </c>
       <c r="Y329" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA329" t="n">
         <v>1</v>
       </c>
-      <c r="Z329" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA329" t="n">
-        <v>0</v>
-      </c>
       <c r="AB329" t="n">
-        <v>0.6035</v>
+        <v>0.6052999999999999</v>
       </c>
     </row>
     <row r="330">
@@ -30105,37 +30105,37 @@
         <v>2013</v>
       </c>
       <c r="D330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E330" t="n">
         <v>1</v>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G330" t="n">
         <v>1</v>
       </c>
       <c r="H330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I330" t="n">
         <v>1</v>
       </c>
       <c r="J330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K330" t="n">
         <v>1</v>
       </c>
       <c r="L330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M330" t="n">
         <v>1</v>
       </c>
       <c r="N330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O330" t="n">
         <v>1</v>
@@ -30162,7 +30162,7 @@
         <v>0</v>
       </c>
       <c r="W330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X330" t="n">
         <v>0</v>
@@ -30174,10 +30174,10 @@
         <v>0</v>
       </c>
       <c r="AA330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB330" t="n">
-        <v>0.6237</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="331">
@@ -42435,40 +42435,40 @@
         <v>1995</v>
       </c>
       <c r="D467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P467" t="n">
         <v>0</v>
@@ -42492,13 +42492,13 @@
         <v>0</v>
       </c>
       <c r="W467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X467" t="n">
         <v>0</v>
       </c>
       <c r="Y467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z467" t="n">
         <v>0</v>
@@ -42507,7 +42507,7 @@
         <v>0</v>
       </c>
       <c r="AB467" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="468">
@@ -42885,40 +42885,40 @@
         <v>2000</v>
       </c>
       <c r="D472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P472" t="n">
         <v>0</v>
@@ -42939,7 +42939,7 @@
         <v>0</v>
       </c>
       <c r="V472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W472" t="n">
         <v>0</v>
@@ -42948,7 +42948,7 @@
         <v>0</v>
       </c>
       <c r="Y472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z472" t="n">
         <v>0</v>
@@ -42957,7 +42957,7 @@
         <v>0</v>
       </c>
       <c r="AB472" t="n">
-        <v>0</v>
+        <v>0.5208</v>
       </c>
     </row>
     <row r="473">
@@ -43245,40 +43245,40 @@
         <v>2004</v>
       </c>
       <c r="D476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P476" t="n">
         <v>0</v>
@@ -43296,7 +43296,7 @@
         <v>0</v>
       </c>
       <c r="U476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V476" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
         <v>0</v>
       </c>
       <c r="X476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y476" t="n">
         <v>0</v>
@@ -43317,7 +43317,7 @@
         <v>0</v>
       </c>
       <c r="AB476" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="477">
@@ -43335,40 +43335,40 @@
         <v>2005</v>
       </c>
       <c r="D477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P477" t="n">
         <v>0</v>
@@ -43383,10 +43383,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V477" t="n">
         <v>0</v>
@@ -43398,7 +43398,7 @@
         <v>0</v>
       </c>
       <c r="Y477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z477" t="n">
         <v>0</v>
@@ -43407,7 +43407,7 @@
         <v>0</v>
       </c>
       <c r="AB477" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="478">
@@ -43473,7 +43473,7 @@
         <v>0</v>
       </c>
       <c r="T478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U478" t="n">
         <v>0</v>
@@ -43515,40 +43515,40 @@
         <v>2007</v>
       </c>
       <c r="D479" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F479" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H479" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J479" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L479" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N479" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P479" t="n">
         <v>0</v>
@@ -43563,31 +43563,31 @@
         <v>0</v>
       </c>
       <c r="T479" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V479" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X479" t="n">
         <v>0</v>
       </c>
       <c r="Y479" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA479" t="n">
         <v>0</v>
       </c>
       <c r="AB479" t="n">
-        <v>0</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="480">
@@ -43605,40 +43605,40 @@
         <v>2008</v>
       </c>
       <c r="D480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P480" t="n">
         <v>0</v>
@@ -43656,7 +43656,7 @@
         <v>0</v>
       </c>
       <c r="U480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V480" t="n">
         <v>0</v>
@@ -43674,10 +43674,10 @@
         <v>0</v>
       </c>
       <c r="AA480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB480" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="481">
@@ -43785,40 +43785,40 @@
         <v>2010</v>
       </c>
       <c r="D482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P482" t="n">
         <v>0</v>
@@ -43836,7 +43836,7 @@
         <v>0</v>
       </c>
       <c r="U482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V482" t="n">
         <v>0</v>
@@ -43848,7 +43848,7 @@
         <v>0</v>
       </c>
       <c r="Y482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z482" t="n">
         <v>0</v>
@@ -43857,7 +43857,7 @@
         <v>0</v>
       </c>
       <c r="AB482" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="483">
@@ -43875,16 +43875,16 @@
         <v>2011</v>
       </c>
       <c r="D483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -43899,16 +43899,16 @@
         <v>0</v>
       </c>
       <c r="L483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P483" t="n">
         <v>0</v>
@@ -43923,7 +43923,7 @@
         <v>0</v>
       </c>
       <c r="T483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U483" t="n">
         <v>0</v>
@@ -43932,7 +43932,7 @@
         <v>0</v>
       </c>
       <c r="W483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X483" t="n">
         <v>0</v>
@@ -43944,10 +43944,10 @@
         <v>0</v>
       </c>
       <c r="AA483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB483" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="484">
@@ -43965,40 +43965,40 @@
         <v>2012</v>
       </c>
       <c r="D484" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F484" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H484" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J484" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L484" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N484" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P484" t="n">
         <v>0</v>
@@ -44016,10 +44016,10 @@
         <v>0</v>
       </c>
       <c r="U484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V484" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W484" t="n">
         <v>0</v>
@@ -44028,16 +44028,16 @@
         <v>0</v>
       </c>
       <c r="Y484" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z484" t="n">
         <v>0</v>
       </c>
       <c r="AA484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB484" t="n">
-        <v>0</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="485">
@@ -44103,7 +44103,7 @@
         <v>0</v>
       </c>
       <c r="T485" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U485" t="n">
         <v>0</v>
@@ -44235,40 +44235,40 @@
         <v>2015</v>
       </c>
       <c r="D487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P487" t="n">
         <v>0</v>
@@ -44286,7 +44286,7 @@
         <v>0</v>
       </c>
       <c r="U487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V487" t="n">
         <v>0</v>
@@ -44304,10 +44304,10 @@
         <v>0</v>
       </c>
       <c r="AA487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB487" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="488">
@@ -44415,16 +44415,16 @@
         <v>2017</v>
       </c>
       <c r="D489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -44439,16 +44439,16 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P489" t="n">
         <v>0</v>
@@ -44463,10 +44463,10 @@
         <v>0</v>
       </c>
       <c r="T489" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V489" t="n">
         <v>0</v>
@@ -44484,10 +44484,10 @@
         <v>0</v>
       </c>
       <c r="AA489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB489" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="490">
@@ -44733,7 +44733,7 @@
         <v>0</v>
       </c>
       <c r="T492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U492" t="n">
         <v>0</v>
@@ -44775,40 +44775,40 @@
         <v>2021</v>
       </c>
       <c r="D493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P493" t="n">
         <v>0</v>
@@ -44826,7 +44826,7 @@
         <v>0</v>
       </c>
       <c r="U493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V493" t="n">
         <v>0</v>
@@ -44838,7 +44838,7 @@
         <v>0</v>
       </c>
       <c r="Y493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z493" t="n">
         <v>0</v>
@@ -44847,7 +44847,7 @@
         <v>0</v>
       </c>
       <c r="AB493" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="494">

--- a/Data/output/reforms/output/reform_panel.xlsx
+++ b/Data/output/reforms/output/reform_panel.xlsx
@@ -30015,13 +30015,13 @@
         <v>2012</v>
       </c>
       <c r="D329" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E329" t="n">
         <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G329" t="n">
         <v>1</v>
@@ -30039,13 +30039,13 @@
         <v>1</v>
       </c>
       <c r="L329" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M329" t="n">
         <v>1</v>
       </c>
       <c r="N329" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O329" t="n">
         <v>1</v>
@@ -30066,13 +30066,13 @@
         <v>0</v>
       </c>
       <c r="U329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V329" t="n">
         <v>1</v>
       </c>
       <c r="W329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X329" t="n">
         <v>0</v>
@@ -30084,10 +30084,10 @@
         <v>0</v>
       </c>
       <c r="AA329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB329" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="330">
@@ -30195,40 +30195,40 @@
         <v>2014</v>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -30246,7 +30246,7 @@
         <v>0</v>
       </c>
       <c r="U331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V331" t="n">
         <v>0</v>
@@ -30255,7 +30255,7 @@
         <v>0</v>
       </c>
       <c r="X331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y331" t="n">
         <v>0</v>
@@ -30267,7 +30267,7 @@
         <v>0</v>
       </c>
       <c r="AB331" t="n">
-        <v>0.6035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">

--- a/Data/output/reforms/output/reform_panel.xlsx
+++ b/Data/output/reforms/output/reform_panel.xlsx
@@ -42435,13 +42435,13 @@
         <v>1995</v>
       </c>
       <c r="D467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E467" t="n">
         <v>1</v>
       </c>
       <c r="F467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G467" t="n">
         <v>1</v>
@@ -42459,13 +42459,13 @@
         <v>1</v>
       </c>
       <c r="L467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M467" t="n">
         <v>1</v>
       </c>
       <c r="N467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O467" t="n">
         <v>1</v>
@@ -42492,7 +42492,7 @@
         <v>0</v>
       </c>
       <c r="W467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X467" t="n">
         <v>0</v>
@@ -42504,10 +42504,10 @@
         <v>0</v>
       </c>
       <c r="AA467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB467" t="n">
-        <v>0.6035</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="468">
@@ -42525,40 +42525,40 @@
         <v>1996</v>
       </c>
       <c r="D468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P468" t="n">
         <v>0</v>
@@ -42573,31 +42573,31 @@
         <v>0</v>
       </c>
       <c r="T468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U468" t="n">
         <v>0</v>
       </c>
       <c r="V468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W468" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X468" t="n">
         <v>0</v>
       </c>
       <c r="Y468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB468" t="n">
-        <v>0</v>
+        <v>0.5404</v>
       </c>
     </row>
     <row r="469">
@@ -42705,40 +42705,40 @@
         <v>1998</v>
       </c>
       <c r="D470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P470" t="n">
         <v>0</v>
@@ -42753,31 +42753,31 @@
         <v>0</v>
       </c>
       <c r="T470" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W470" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X470" t="n">
         <v>0</v>
       </c>
       <c r="Y470" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB470" t="n">
-        <v>0</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="471">
@@ -42795,40 +42795,40 @@
         <v>1999</v>
       </c>
       <c r="D471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P471" t="n">
         <v>0</v>
@@ -42846,10 +42846,10 @@
         <v>0</v>
       </c>
       <c r="U471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W471" t="n">
         <v>0</v>
@@ -42858,7 +42858,7 @@
         <v>0</v>
       </c>
       <c r="Y471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z471" t="n">
         <v>0</v>
@@ -42867,7 +42867,7 @@
         <v>0</v>
       </c>
       <c r="AB471" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="472">
@@ -42885,37 +42885,37 @@
         <v>2000</v>
       </c>
       <c r="D472" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E472" t="n">
         <v>1</v>
       </c>
       <c r="F472" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G472" t="n">
         <v>1</v>
       </c>
       <c r="H472" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I472" t="n">
         <v>1</v>
       </c>
       <c r="J472" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K472" t="n">
         <v>1</v>
       </c>
       <c r="L472" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M472" t="n">
         <v>1</v>
       </c>
       <c r="N472" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O472" t="n">
         <v>1</v>
@@ -42933,31 +42933,31 @@
         <v>0</v>
       </c>
       <c r="T472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V472" t="n">
         <v>2</v>
       </c>
       <c r="W472" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X472" t="n">
         <v>0</v>
       </c>
       <c r="Y472" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA472" t="n">
         <v>2</v>
       </c>
-      <c r="Z472" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA472" t="n">
-        <v>0</v>
-      </c>
       <c r="AB472" t="n">
-        <v>0.5208</v>
+        <v>0.7133</v>
       </c>
     </row>
     <row r="473">
@@ -43065,16 +43065,16 @@
         <v>2002</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -43089,16 +43089,16 @@
         <v>0</v>
       </c>
       <c r="L474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P474" t="n">
         <v>0</v>
@@ -43113,13 +43113,13 @@
         <v>0</v>
       </c>
       <c r="T474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U474" t="n">
         <v>0</v>
       </c>
       <c r="V474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W474" t="n">
         <v>0</v>
@@ -43134,10 +43134,10 @@
         <v>0</v>
       </c>
       <c r="AA474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB474" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="475">
@@ -43155,40 +43155,40 @@
         <v>2003</v>
       </c>
       <c r="D475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P475" t="n">
         <v>0</v>
@@ -43206,28 +43206,28 @@
         <v>0</v>
       </c>
       <c r="U475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V475" t="n">
         <v>0</v>
       </c>
       <c r="W475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X475" t="n">
         <v>0</v>
       </c>
       <c r="Y475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z475" t="n">
         <v>0</v>
       </c>
       <c r="AA475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB475" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="476">
@@ -43293,7 +43293,7 @@
         <v>0</v>
       </c>
       <c r="T476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U476" t="n">
         <v>1</v>
@@ -43305,10 +43305,10 @@
         <v>0</v>
       </c>
       <c r="X476" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y476" t="n">
         <v>1</v>
-      </c>
-      <c r="Y476" t="n">
-        <v>0</v>
       </c>
       <c r="Z476" t="n">
         <v>0</v>
@@ -43473,7 +43473,7 @@
         <v>0</v>
       </c>
       <c r="T478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U478" t="n">
         <v>0</v>
@@ -43515,37 +43515,37 @@
         <v>2007</v>
       </c>
       <c r="D479" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E479" t="n">
         <v>1</v>
       </c>
       <c r="F479" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G479" t="n">
         <v>1</v>
       </c>
       <c r="H479" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I479" t="n">
         <v>1</v>
       </c>
       <c r="J479" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K479" t="n">
         <v>1</v>
       </c>
       <c r="L479" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M479" t="n">
         <v>1</v>
       </c>
       <c r="N479" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O479" t="n">
         <v>1</v>
@@ -43569,7 +43569,7 @@
         <v>1</v>
       </c>
       <c r="V479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W479" t="n">
         <v>1</v>
@@ -43578,7 +43578,7 @@
         <v>0</v>
       </c>
       <c r="Y479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z479" t="n">
         <v>1</v>
@@ -43587,7 +43587,7 @@
         <v>0</v>
       </c>
       <c r="AB479" t="n">
-        <v>0.7615</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="480">
@@ -43605,40 +43605,40 @@
         <v>2008</v>
       </c>
       <c r="D480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P480" t="n">
         <v>0</v>
@@ -43656,7 +43656,7 @@
         <v>0</v>
       </c>
       <c r="U480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V480" t="n">
         <v>0</v>
@@ -43674,10 +43674,10 @@
         <v>0</v>
       </c>
       <c r="AA480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB480" t="n">
-        <v>0.6035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -43785,40 +43785,40 @@
         <v>2010</v>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P482" t="n">
         <v>0</v>
@@ -43836,7 +43836,7 @@
         <v>0</v>
       </c>
       <c r="U482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V482" t="n">
         <v>0</v>
@@ -43848,7 +43848,7 @@
         <v>0</v>
       </c>
       <c r="Y482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z482" t="n">
         <v>0</v>
@@ -43857,7 +43857,7 @@
         <v>0</v>
       </c>
       <c r="AB482" t="n">
-        <v>0.6035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -43875,16 +43875,16 @@
         <v>2011</v>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -43899,16 +43899,16 @@
         <v>0</v>
       </c>
       <c r="L483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P483" t="n">
         <v>0</v>
@@ -43932,7 +43932,7 @@
         <v>0</v>
       </c>
       <c r="W483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X483" t="n">
         <v>0</v>
@@ -43944,10 +43944,10 @@
         <v>0</v>
       </c>
       <c r="AA483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB483" t="n">
-        <v>0.3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484">
@@ -44055,40 +44055,40 @@
         <v>2013</v>
       </c>
       <c r="D485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P485" t="n">
         <v>0</v>
@@ -44112,7 +44112,7 @@
         <v>0</v>
       </c>
       <c r="W485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X485" t="n">
         <v>0</v>
@@ -44127,7 +44127,7 @@
         <v>0</v>
       </c>
       <c r="AB485" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="486">
@@ -44415,13 +44415,13 @@
         <v>2017</v>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E489" t="n">
         <v>1</v>
       </c>
       <c r="F489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G489" t="n">
         <v>1</v>
@@ -44439,13 +44439,13 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M489" t="n">
         <v>1</v>
       </c>
       <c r="N489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O489" t="n">
         <v>1</v>
@@ -44472,7 +44472,7 @@
         <v>0</v>
       </c>
       <c r="W489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X489" t="n">
         <v>0</v>
@@ -44484,10 +44484,10 @@
         <v>0</v>
       </c>
       <c r="AA489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB489" t="n">
-        <v>0.3535</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="490">
@@ -44505,16 +44505,16 @@
         <v>2018</v>
       </c>
       <c r="D490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -44529,16 +44529,16 @@
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P490" t="n">
         <v>0</v>
@@ -44562,7 +44562,7 @@
         <v>0</v>
       </c>
       <c r="W490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X490" t="n">
         <v>0</v>
@@ -44574,10 +44574,10 @@
         <v>0</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB490" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="491">
@@ -44685,40 +44685,40 @@
         <v>2020</v>
       </c>
       <c r="D492" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F492" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H492" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J492" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L492" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N492" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P492" t="n">
         <v>0</v>
@@ -44733,22 +44733,22 @@
         <v>0</v>
       </c>
       <c r="T492" t="n">
+        <v>8</v>
+      </c>
+      <c r="U492" t="n">
+        <v>4</v>
+      </c>
+      <c r="V492" t="n">
         <v>1</v>
       </c>
-      <c r="U492" t="n">
-        <v>0</v>
-      </c>
-      <c r="V492" t="n">
-        <v>0</v>
-      </c>
       <c r="W492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X492" t="n">
         <v>0</v>
       </c>
       <c r="Y492" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z492" t="n">
         <v>0</v>
@@ -44757,7 +44757,7 @@
         <v>0</v>
       </c>
       <c r="AB492" t="n">
-        <v>0</v>
+        <v>0.7029</v>
       </c>
     </row>
     <row r="493">
@@ -44775,37 +44775,37 @@
         <v>2021</v>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E493" t="n">
         <v>1</v>
       </c>
       <c r="F493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G493" t="n">
         <v>1</v>
       </c>
       <c r="H493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I493" t="n">
         <v>1</v>
       </c>
       <c r="J493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K493" t="n">
         <v>1</v>
       </c>
       <c r="L493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M493" t="n">
         <v>1</v>
       </c>
       <c r="N493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O493" t="n">
         <v>1</v>
@@ -44823,13 +44823,13 @@
         <v>0</v>
       </c>
       <c r="T493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U493" t="n">
         <v>1</v>
       </c>
       <c r="V493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W493" t="n">
         <v>0</v>
@@ -44838,7 +44838,7 @@
         <v>0</v>
       </c>
       <c r="Y493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z493" t="n">
         <v>0</v>
@@ -44847,7 +44847,7 @@
         <v>0</v>
       </c>
       <c r="AB493" t="n">
-        <v>0.6035</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="494">
@@ -44865,40 +44865,40 @@
         <v>2022</v>
       </c>
       <c r="D494" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F494" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H494" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J494" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L494" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N494" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P494" t="n">
         <v>0</v>
@@ -44913,31 +44913,31 @@
         <v>0</v>
       </c>
       <c r="T494" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X494" t="n">
         <v>0</v>
       </c>
       <c r="Y494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB494" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="495">
@@ -44955,40 +44955,40 @@
         <v>2023</v>
       </c>
       <c r="D495" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F495" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L495" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N495" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P495" t="n">
         <v>0</v>
@@ -45003,13 +45003,13 @@
         <v>0</v>
       </c>
       <c r="T495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W495" t="n">
         <v>0</v>
@@ -45018,16 +45018,16 @@
         <v>0</v>
       </c>
       <c r="Y495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z495" t="n">
         <v>0</v>
       </c>
       <c r="AA495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB495" t="n">
-        <v>0</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="496">
@@ -45045,40 +45045,40 @@
         <v>2024</v>
       </c>
       <c r="D496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P496" t="n">
         <v>0</v>
@@ -45093,7 +45093,7 @@
         <v>0</v>
       </c>
       <c r="T496" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U496" t="n">
         <v>0</v>
@@ -45102,7 +45102,7 @@
         <v>0</v>
       </c>
       <c r="W496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X496" t="n">
         <v>0</v>
@@ -45114,10 +45114,10 @@
         <v>0</v>
       </c>
       <c r="AA496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB496" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="497">
@@ -45183,7 +45183,7 @@
         <v>0</v>
       </c>
       <c r="T497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U497" t="n">
         <v>0</v>

--- a/Data/output/reforms/output/reform_panel.xlsx
+++ b/Data/output/reforms/output/reform_panel.xlsx
@@ -25695,40 +25695,40 @@
         <v>1995</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -25752,22 +25752,22 @@
         <v>0</v>
       </c>
       <c r="W281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X281" t="n">
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="282">
@@ -25785,16 +25785,16 @@
         <v>1996</v>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -25809,16 +25809,16 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P282" t="n">
         <v>0</v>
@@ -25833,10 +25833,10 @@
         <v>0</v>
       </c>
       <c r="T282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V282" t="n">
         <v>0</v>
@@ -25851,13 +25851,13 @@
         <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="283">
@@ -25875,10 +25875,10 @@
         <v>1997</v>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F283" t="n">
         <v>0</v>
@@ -25899,10 +25899,10 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N283" t="n">
         <v>0</v>
@@ -25923,10 +25923,10 @@
         <v>0</v>
       </c>
       <c r="T283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V283" t="n">
         <v>0</v>
@@ -25947,7 +25947,7 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="284">
@@ -25965,16 +25965,16 @@
         <v>1998</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -25989,16 +25989,16 @@
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -26016,7 +26016,7 @@
         <v>0</v>
       </c>
       <c r="U284" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V284" t="n">
         <v>0</v>
@@ -26028,16 +26028,16 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z284" t="n">
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB284" t="n">
-        <v>0</v>
+        <v>0.4883</v>
       </c>
     </row>
     <row r="285">
@@ -26055,40 +26055,40 @@
         <v>1999</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P285" t="n">
         <v>0</v>
@@ -26103,31 +26103,31 @@
         <v>0</v>
       </c>
       <c r="T285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V285" t="n">
         <v>0</v>
       </c>
       <c r="W285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X285" t="n">
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z285" t="n">
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB285" t="n">
-        <v>0</v>
+        <v>0.7383</v>
       </c>
     </row>
     <row r="286">
@@ -26145,16 +26145,16 @@
         <v>2000</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -26169,16 +26169,16 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P286" t="n">
         <v>0</v>
@@ -26193,13 +26193,13 @@
         <v>0</v>
       </c>
       <c r="T286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U286" t="n">
         <v>0</v>
       </c>
       <c r="V286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W286" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z286" t="n">
         <v>0</v>
@@ -26217,7 +26217,7 @@
         <v>0</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="287">
@@ -26235,40 +26235,40 @@
         <v>2001</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -26283,13 +26283,13 @@
         <v>0</v>
       </c>
       <c r="T287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U287" t="n">
         <v>0</v>
       </c>
       <c r="V287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W287" t="n">
         <v>0</v>
@@ -26307,7 +26307,7 @@
         <v>0</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="288">
@@ -26325,40 +26325,40 @@
         <v>2002</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -26379,25 +26379,25 @@
         <v>0</v>
       </c>
       <c r="V288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X288" t="n">
         <v>0</v>
       </c>
       <c r="Y288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA288" t="n">
         <v>0</v>
       </c>
       <c r="AB288" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="289">
@@ -26415,16 +26415,16 @@
         <v>2003</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -26439,16 +26439,16 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -26469,7 +26469,7 @@
         <v>0</v>
       </c>
       <c r="V289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W289" t="n">
         <v>0</v>
@@ -26481,13 +26481,13 @@
         <v>0</v>
       </c>
       <c r="Z289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA289" t="n">
         <v>0</v>
       </c>
       <c r="AB289" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="290">
@@ -26505,40 +26505,40 @@
         <v>2004</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -26553,10 +26553,10 @@
         <v>0</v>
       </c>
       <c r="T290" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V290" t="n">
         <v>0</v>
@@ -26568,7 +26568,7 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z290" t="n">
         <v>0</v>
@@ -26577,7 +26577,7 @@
         <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="291">
@@ -26595,46 +26595,46 @@
         <v>2005</v>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R291" t="n">
         <v>0</v>
@@ -26646,19 +26646,19 @@
         <v>0</v>
       </c>
       <c r="U291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V291" t="n">
         <v>0</v>
       </c>
       <c r="W291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X291" t="n">
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z291" t="n">
         <v>0</v>
@@ -26667,7 +26667,7 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="292">
@@ -26685,40 +26685,40 @@
         <v>2006</v>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -26733,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="T292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U292" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V292" t="n">
         <v>0</v>
@@ -26748,7 +26748,7 @@
         <v>0</v>
       </c>
       <c r="Y292" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z292" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>0</v>
+        <v>0.6493</v>
       </c>
     </row>
     <row r="293">
@@ -26775,40 +26775,40 @@
         <v>2007</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P293" t="n">
         <v>0</v>
@@ -26826,19 +26826,19 @@
         <v>0</v>
       </c>
       <c r="U293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V293" t="n">
         <v>0</v>
       </c>
       <c r="W293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X293" t="n">
         <v>0</v>
       </c>
       <c r="Y293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z293" t="n">
         <v>0</v>
@@ -26847,7 +26847,7 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="294">
@@ -26865,40 +26865,40 @@
         <v>2008</v>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -26913,10 +26913,10 @@
         <v>0</v>
       </c>
       <c r="T294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V294" t="n">
         <v>0</v>
@@ -26925,10 +26925,10 @@
         <v>0</v>
       </c>
       <c r="X294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z294" t="n">
         <v>0</v>
@@ -26937,7 +26937,7 @@
         <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="295">
@@ -26955,40 +26955,40 @@
         <v>2009</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -27012,13 +27012,13 @@
         <v>0</v>
       </c>
       <c r="W295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X295" t="n">
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z295" t="n">
         <v>0</v>
@@ -27027,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="296">
@@ -27045,16 +27045,16 @@
         <v>2010</v>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -27069,16 +27069,16 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -27093,13 +27093,13 @@
         <v>0</v>
       </c>
       <c r="T296" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U296" t="n">
         <v>0</v>
       </c>
       <c r="V296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W296" t="n">
         <v>0</v>
@@ -27117,7 +27117,7 @@
         <v>0</v>
       </c>
       <c r="AB296" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="297">
@@ -27135,40 +27135,40 @@
         <v>2011</v>
       </c>
       <c r="D297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -27186,7 +27186,7 @@
         <v>0</v>
       </c>
       <c r="U297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V297" t="n">
         <v>0</v>
@@ -27198,7 +27198,7 @@
         <v>0</v>
       </c>
       <c r="Y297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z297" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
         <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="298">
@@ -27225,16 +27225,16 @@
         <v>2012</v>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -27249,16 +27249,16 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -27273,13 +27273,13 @@
         <v>0</v>
       </c>
       <c r="T298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U298" t="n">
         <v>0</v>
       </c>
       <c r="V298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W298" t="n">
         <v>0</v>
@@ -27291,13 +27291,13 @@
         <v>0</v>
       </c>
       <c r="Z298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA298" t="n">
         <v>0</v>
       </c>
       <c r="AB298" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="299">
@@ -27315,16 +27315,16 @@
         <v>2013</v>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -27339,16 +27339,16 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -27366,7 +27366,7 @@
         <v>0</v>
       </c>
       <c r="U299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V299" t="n">
         <v>0</v>
@@ -27378,7 +27378,7 @@
         <v>0</v>
       </c>
       <c r="Y299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z299" t="n">
         <v>0</v>
@@ -27387,7 +27387,7 @@
         <v>0</v>
       </c>
       <c r="AB299" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="300">
@@ -27453,7 +27453,7 @@
         <v>0</v>
       </c>
       <c r="T300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U300" t="n">
         <v>0</v>
@@ -27495,16 +27495,16 @@
         <v>2015</v>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -27519,16 +27519,16 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P301" t="n">
         <v>0</v>
@@ -27546,7 +27546,7 @@
         <v>0</v>
       </c>
       <c r="U301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V301" t="n">
         <v>0</v>
@@ -27564,10 +27564,10 @@
         <v>0</v>
       </c>
       <c r="AA301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB301" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="302">
@@ -27585,40 +27585,40 @@
         <v>2016</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -27633,13 +27633,13 @@
         <v>0</v>
       </c>
       <c r="T302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U302" t="n">
         <v>0</v>
       </c>
       <c r="V302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W302" t="n">
         <v>0</v>
@@ -27651,13 +27651,13 @@
         <v>0</v>
       </c>
       <c r="Z302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA302" t="n">
         <v>0</v>
       </c>
       <c r="AB302" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="303">
@@ -27675,16 +27675,16 @@
         <v>2017</v>
       </c>
       <c r="D303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -27699,16 +27699,16 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -27729,7 +27729,7 @@
         <v>0</v>
       </c>
       <c r="V303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W303" t="n">
         <v>0</v>
@@ -27741,13 +27741,13 @@
         <v>0</v>
       </c>
       <c r="Z303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA303" t="n">
         <v>0</v>
       </c>
       <c r="AB303" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="304">
@@ -27813,7 +27813,7 @@
         <v>0</v>
       </c>
       <c r="T304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U304" t="n">
         <v>0</v>
@@ -27855,40 +27855,40 @@
         <v>2019</v>
       </c>
       <c r="D305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P305" t="n">
         <v>0</v>
@@ -27909,25 +27909,25 @@
         <v>0</v>
       </c>
       <c r="V305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W305" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X305" t="n">
         <v>0</v>
       </c>
       <c r="Y305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z305" t="n">
         <v>0</v>
       </c>
       <c r="AA305" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB305" t="n">
-        <v>0</v>
+        <v>0.5404</v>
       </c>
     </row>
     <row r="306">
@@ -27945,40 +27945,40 @@
         <v>2020</v>
       </c>
       <c r="D306" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J306" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L306" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -27993,31 +27993,31 @@
         <v>0</v>
       </c>
       <c r="T306" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U306" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X306" t="n">
         <v>0</v>
       </c>
       <c r="Y306" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z306" t="n">
         <v>0</v>
       </c>
       <c r="AA306" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB306" t="n">
-        <v>0</v>
+        <v>0.7347</v>
       </c>
     </row>
     <row r="307">
@@ -28035,40 +28035,40 @@
         <v>2021</v>
       </c>
       <c r="D307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -28086,28 +28086,28 @@
         <v>0</v>
       </c>
       <c r="U307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V307" t="n">
         <v>0</v>
       </c>
       <c r="W307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X307" t="n">
         <v>0</v>
       </c>
       <c r="Y307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB307" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="308">
@@ -28125,40 +28125,40 @@
         <v>2022</v>
       </c>
       <c r="D308" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N308" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -28176,28 +28176,28 @@
         <v>0</v>
       </c>
       <c r="U308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V308" t="n">
         <v>0</v>
       </c>
       <c r="W308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X308" t="n">
         <v>0</v>
       </c>
       <c r="Y308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z308" t="n">
         <v>0</v>
       </c>
       <c r="AA308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB308" t="n">
-        <v>0</v>
+        <v>0.6931</v>
       </c>
     </row>
     <row r="309">
@@ -28215,40 +28215,40 @@
         <v>2023</v>
       </c>
       <c r="D309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P309" t="n">
         <v>0</v>
@@ -28263,10 +28263,10 @@
         <v>0</v>
       </c>
       <c r="T309" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V309" t="n">
         <v>0</v>
@@ -28284,10 +28284,10 @@
         <v>0</v>
       </c>
       <c r="AA309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB309" t="n">
-        <v>0</v>
+        <v>0.6458</v>
       </c>
     </row>
     <row r="310">
@@ -28305,40 +28305,40 @@
         <v>2024</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -28353,7 +28353,7 @@
         <v>0</v>
       </c>
       <c r="T310" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U310" t="n">
         <v>0</v>
@@ -28362,7 +28362,7 @@
         <v>0</v>
       </c>
       <c r="W310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X310" t="n">
         <v>0</v>
@@ -28371,13 +28371,13 @@
         <v>0</v>
       </c>
       <c r="Z310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA310" t="n">
         <v>0</v>
       </c>
       <c r="AB310" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="311">
@@ -28443,7 +28443,7 @@
         <v>0</v>
       </c>
       <c r="T311" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U311" t="n">
         <v>0</v>
@@ -30555,79 +30555,79 @@
         <v>2018</v>
       </c>
       <c r="D335" t="n">
+        <v>4</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" t="n">
+        <v>4</v>
+      </c>
+      <c r="G335" t="n">
+        <v>1</v>
+      </c>
+      <c r="H335" t="n">
+        <v>1</v>
+      </c>
+      <c r="I335" t="n">
+        <v>1</v>
+      </c>
+      <c r="J335" t="n">
+        <v>1</v>
+      </c>
+      <c r="K335" t="n">
+        <v>1</v>
+      </c>
+      <c r="L335" t="n">
+        <v>4</v>
+      </c>
+      <c r="M335" t="n">
+        <v>1</v>
+      </c>
+      <c r="N335" t="n">
+        <v>4</v>
+      </c>
+      <c r="O335" t="n">
+        <v>1</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>0</v>
+      </c>
+      <c r="R335" t="n">
+        <v>0</v>
+      </c>
+      <c r="S335" t="n">
+        <v>0</v>
+      </c>
+      <c r="T335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="n">
+        <v>0</v>
+      </c>
+      <c r="V335" t="n">
+        <v>1</v>
+      </c>
+      <c r="W335" t="n">
         <v>3</v>
       </c>
-      <c r="E335" t="n">
-        <v>1</v>
-      </c>
-      <c r="F335" t="n">
-        <v>3</v>
-      </c>
-      <c r="G335" t="n">
-        <v>1</v>
-      </c>
-      <c r="H335" t="n">
-        <v>0</v>
-      </c>
-      <c r="I335" t="n">
-        <v>0</v>
-      </c>
-      <c r="J335" t="n">
-        <v>0</v>
-      </c>
-      <c r="K335" t="n">
-        <v>0</v>
-      </c>
-      <c r="L335" t="n">
-        <v>3</v>
-      </c>
-      <c r="M335" t="n">
-        <v>1</v>
-      </c>
-      <c r="N335" t="n">
-        <v>3</v>
-      </c>
-      <c r="O335" t="n">
-        <v>1</v>
-      </c>
-      <c r="P335" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
-      <c r="R335" t="n">
-        <v>0</v>
-      </c>
-      <c r="S335" t="n">
-        <v>0</v>
-      </c>
-      <c r="T335" t="n">
-        <v>0</v>
-      </c>
-      <c r="U335" t="n">
-        <v>0</v>
-      </c>
-      <c r="V335" t="n">
-        <v>1</v>
-      </c>
-      <c r="W335" t="n">
+      <c r="X335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z335" t="n">
         <v>2</v>
       </c>
-      <c r="X335" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y335" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z335" t="n">
-        <v>1</v>
-      </c>
       <c r="AA335" t="n">
         <v>1</v>
       </c>
       <c r="AB335" t="n">
-        <v>0.4883</v>
+        <v>0.6052999999999999</v>
       </c>
     </row>
     <row r="336">
@@ -30735,40 +30735,40 @@
         <v>2020</v>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P337" t="n">
         <v>0</v>
@@ -30789,16 +30789,16 @@
         <v>0</v>
       </c>
       <c r="V337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X337" t="n">
         <v>0</v>
       </c>
       <c r="Y337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z337" t="n">
         <v>0</v>
@@ -30807,7 +30807,7 @@
         <v>0</v>
       </c>
       <c r="AB337" t="n">
-        <v>0.552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -30825,16 +30825,16 @@
         <v>2021</v>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -30849,16 +30849,16 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P338" t="n">
         <v>0</v>
@@ -30876,7 +30876,7 @@
         <v>4</v>
       </c>
       <c r="U338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V338" t="n">
         <v>0</v>
@@ -30888,7 +30888,7 @@
         <v>0</v>
       </c>
       <c r="Y338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z338" t="n">
         <v>0</v>
@@ -30897,7 +30897,7 @@
         <v>0</v>
       </c>
       <c r="AB338" t="n">
-        <v>0.3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -39645,40 +39645,40 @@
         <v>1995</v>
       </c>
       <c r="D436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P436" t="n">
         <v>0</v>
@@ -39699,25 +39699,25 @@
         <v>0</v>
       </c>
       <c r="V436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X436" t="n">
         <v>0</v>
       </c>
       <c r="Y436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA436" t="n">
         <v>0</v>
       </c>
       <c r="AB436" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="437">
@@ -39735,40 +39735,40 @@
         <v>1996</v>
       </c>
       <c r="D437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P437" t="n">
         <v>0</v>
@@ -39789,10 +39789,10 @@
         <v>0</v>
       </c>
       <c r="V437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X437" t="n">
         <v>0</v>
@@ -39801,13 +39801,13 @@
         <v>0</v>
       </c>
       <c r="Z437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA437" t="n">
         <v>0</v>
       </c>
       <c r="AB437" t="n">
-        <v>0</v>
+        <v>0.5208</v>
       </c>
     </row>
     <row r="438">
@@ -39825,40 +39825,40 @@
         <v>1997</v>
       </c>
       <c r="D438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P438" t="n">
         <v>0</v>
@@ -39876,7 +39876,7 @@
         <v>0</v>
       </c>
       <c r="U438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V438" t="n">
         <v>0</v>
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="Y438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z438" t="n">
         <v>0</v>
@@ -39897,7 +39897,7 @@
         <v>0</v>
       </c>
       <c r="AB438" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="439">
@@ -39915,40 +39915,40 @@
         <v>1998</v>
       </c>
       <c r="D439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P439" t="n">
         <v>0</v>
@@ -39972,13 +39972,13 @@
         <v>0</v>
       </c>
       <c r="W439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X439" t="n">
         <v>0</v>
       </c>
       <c r="Y439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z439" t="n">
         <v>0</v>
@@ -39987,7 +39987,7 @@
         <v>0</v>
       </c>
       <c r="AB439" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="440">
@@ -40005,40 +40005,40 @@
         <v>1999</v>
       </c>
       <c r="D440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P440" t="n">
         <v>0</v>
@@ -40053,13 +40053,13 @@
         <v>0</v>
       </c>
       <c r="T440" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U440" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V440" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W440" t="n">
         <v>0</v>
@@ -40068,16 +40068,16 @@
         <v>0</v>
       </c>
       <c r="Y440" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z440" t="n">
         <v>0</v>
       </c>
       <c r="AA440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB440" t="n">
-        <v>0</v>
+        <v>0.5427999999999999</v>
       </c>
     </row>
     <row r="441">
@@ -40095,40 +40095,40 @@
         <v>2000</v>
       </c>
       <c r="D441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P441" t="n">
         <v>0</v>
@@ -40143,13 +40143,13 @@
         <v>0</v>
       </c>
       <c r="T441" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W441" t="n">
         <v>0</v>
@@ -40161,13 +40161,13 @@
         <v>0</v>
       </c>
       <c r="Z441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB441" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="442">
@@ -40185,40 +40185,40 @@
         <v>2001</v>
       </c>
       <c r="D442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P442" t="n">
         <v>0</v>
@@ -40239,7 +40239,7 @@
         <v>0</v>
       </c>
       <c r="V442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W442" t="n">
         <v>0</v>
@@ -40254,10 +40254,10 @@
         <v>0</v>
       </c>
       <c r="AA442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB442" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="443">
@@ -40275,40 +40275,40 @@
         <v>2002</v>
       </c>
       <c r="D443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P443" t="n">
         <v>0</v>
@@ -40326,7 +40326,7 @@
         <v>0</v>
       </c>
       <c r="U443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V443" t="n">
         <v>0</v>
@@ -40338,7 +40338,7 @@
         <v>0</v>
       </c>
       <c r="Y443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z443" t="n">
         <v>0</v>
@@ -40347,7 +40347,7 @@
         <v>0</v>
       </c>
       <c r="AB443" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="444">
@@ -40365,40 +40365,40 @@
         <v>2003</v>
       </c>
       <c r="D444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P444" t="n">
         <v>0</v>
@@ -40413,7 +40413,7 @@
         <v>0</v>
       </c>
       <c r="T444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U444" t="n">
         <v>0</v>
@@ -40422,13 +40422,13 @@
         <v>0</v>
       </c>
       <c r="W444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X444" t="n">
         <v>0</v>
       </c>
       <c r="Y444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z444" t="n">
         <v>0</v>
@@ -40437,7 +40437,7 @@
         <v>0</v>
       </c>
       <c r="AB444" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="445">
@@ -40455,40 +40455,40 @@
         <v>2004</v>
       </c>
       <c r="D445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P445" t="n">
         <v>0</v>
@@ -40512,13 +40512,13 @@
         <v>0</v>
       </c>
       <c r="W445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X445" t="n">
         <v>0</v>
       </c>
       <c r="Y445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z445" t="n">
         <v>0</v>
@@ -40527,7 +40527,7 @@
         <v>0</v>
       </c>
       <c r="AB445" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="446">
@@ -40593,7 +40593,7 @@
         <v>0</v>
       </c>
       <c r="T446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U446" t="n">
         <v>0</v>
@@ -40635,22 +40635,22 @@
         <v>2006</v>
       </c>
       <c r="D447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J447" t="n">
         <v>0</v>
@@ -40659,16 +40659,16 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P447" t="n">
         <v>0</v>
@@ -40686,19 +40686,19 @@
         <v>0</v>
       </c>
       <c r="U447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V447" t="n">
         <v>0</v>
       </c>
       <c r="W447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X447" t="n">
         <v>0</v>
       </c>
       <c r="Y447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z447" t="n">
         <v>0</v>
@@ -40707,7 +40707,7 @@
         <v>0</v>
       </c>
       <c r="AB447" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="448">
@@ -40725,40 +40725,40 @@
         <v>2007</v>
       </c>
       <c r="D448" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F448" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L448" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N448" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P448" t="n">
         <v>0</v>
@@ -40773,13 +40773,13 @@
         <v>0</v>
       </c>
       <c r="T448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U448" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W448" t="n">
         <v>0</v>
@@ -40788,16 +40788,16 @@
         <v>0</v>
       </c>
       <c r="Y448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA448" t="n">
         <v>0</v>
       </c>
       <c r="AB448" t="n">
-        <v>0</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="449">
@@ -40815,40 +40815,40 @@
         <v>2008</v>
       </c>
       <c r="D449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H449" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J449" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P449" t="n">
         <v>0</v>
@@ -40866,28 +40866,28 @@
         <v>0</v>
       </c>
       <c r="U449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V449" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W449" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X449" t="n">
         <v>0</v>
       </c>
       <c r="Y449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA449" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB449" t="n">
-        <v>0</v>
+        <v>0.7306</v>
       </c>
     </row>
     <row r="450">
@@ -40953,7 +40953,7 @@
         <v>0</v>
       </c>
       <c r="T450" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U450" t="n">
         <v>0</v>
@@ -40995,40 +40995,40 @@
         <v>2010</v>
       </c>
       <c r="D451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P451" t="n">
         <v>0</v>
@@ -41046,19 +41046,19 @@
         <v>0</v>
       </c>
       <c r="U451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V451" t="n">
         <v>0</v>
       </c>
       <c r="W451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X451" t="n">
         <v>0</v>
       </c>
       <c r="Y451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z451" t="n">
         <v>0</v>
@@ -41067,7 +41067,7 @@
         <v>0</v>
       </c>
       <c r="AB451" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="452">
@@ -41085,40 +41085,40 @@
         <v>2011</v>
       </c>
       <c r="D452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P452" t="n">
         <v>0</v>
@@ -41133,10 +41133,10 @@
         <v>0</v>
       </c>
       <c r="T452" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V452" t="n">
         <v>0</v>
@@ -41157,7 +41157,7 @@
         <v>0</v>
       </c>
       <c r="AB452" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="453">
@@ -41265,40 +41265,40 @@
         <v>2013</v>
       </c>
       <c r="D454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P454" t="n">
         <v>0</v>
@@ -41313,7 +41313,7 @@
         <v>0</v>
       </c>
       <c r="T454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U454" t="n">
         <v>0</v>
@@ -41322,22 +41322,22 @@
         <v>0</v>
       </c>
       <c r="W454" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X454" t="n">
         <v>0</v>
       </c>
       <c r="Y454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z454" t="n">
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB454" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="455">
@@ -41355,16 +41355,16 @@
         <v>2014</v>
       </c>
       <c r="D455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -41379,16 +41379,16 @@
         <v>0</v>
       </c>
       <c r="L455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P455" t="n">
         <v>0</v>
@@ -41406,7 +41406,7 @@
         <v>0</v>
       </c>
       <c r="U455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V455" t="n">
         <v>0</v>
@@ -41418,7 +41418,7 @@
         <v>0</v>
       </c>
       <c r="Y455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z455" t="n">
         <v>0</v>
@@ -41427,7 +41427,7 @@
         <v>0</v>
       </c>
       <c r="AB455" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="456">
@@ -41445,40 +41445,40 @@
         <v>2015</v>
       </c>
       <c r="D456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P456" t="n">
         <v>0</v>
@@ -41493,22 +41493,22 @@
         <v>0</v>
       </c>
       <c r="T456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V456" t="n">
         <v>0</v>
       </c>
       <c r="W456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X456" t="n">
         <v>0</v>
       </c>
       <c r="Y456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z456" t="n">
         <v>0</v>
@@ -41517,7 +41517,7 @@
         <v>0</v>
       </c>
       <c r="AB456" t="n">
-        <v>0</v>
+        <v>0.6458</v>
       </c>
     </row>
     <row r="457">
@@ -41625,40 +41625,40 @@
         <v>2017</v>
       </c>
       <c r="D458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P458" t="n">
         <v>0</v>
@@ -41676,7 +41676,7 @@
         <v>0</v>
       </c>
       <c r="U458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V458" t="n">
         <v>0</v>
@@ -41688,7 +41688,7 @@
         <v>0</v>
       </c>
       <c r="Y458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z458" t="n">
         <v>0</v>
@@ -41697,7 +41697,7 @@
         <v>0</v>
       </c>
       <c r="AB458" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="459">
@@ -41715,40 +41715,40 @@
         <v>2018</v>
       </c>
       <c r="D459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H459" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J459" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P459" t="n">
         <v>0</v>
@@ -41766,19 +41766,19 @@
         <v>0</v>
       </c>
       <c r="U459" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V459" t="n">
         <v>0</v>
       </c>
       <c r="W459" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X459" t="n">
         <v>0</v>
       </c>
       <c r="Y459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z459" t="n">
         <v>0</v>
@@ -41787,7 +41787,7 @@
         <v>0</v>
       </c>
       <c r="AB459" t="n">
-        <v>0</v>
+        <v>0.6993</v>
       </c>
     </row>
     <row r="460">
@@ -41805,16 +41805,16 @@
         <v>2019</v>
       </c>
       <c r="D460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -41829,16 +41829,16 @@
         <v>0</v>
       </c>
       <c r="L460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P460" t="n">
         <v>0</v>
@@ -41853,10 +41853,10 @@
         <v>0</v>
       </c>
       <c r="T460" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V460" t="n">
         <v>0</v>
@@ -41874,10 +41874,10 @@
         <v>0</v>
       </c>
       <c r="AA460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB460" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="461">
@@ -41985,40 +41985,40 @@
         <v>2021</v>
       </c>
       <c r="D462" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F462" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H462" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J462" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P462" t="n">
         <v>0</v>
@@ -42033,31 +42033,31 @@
         <v>0</v>
       </c>
       <c r="T462" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U462" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V462" t="n">
         <v>0</v>
       </c>
       <c r="W462" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y462" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA462" t="n">
         <v>0</v>
       </c>
       <c r="AB462" t="n">
-        <v>0</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="463">
@@ -42075,40 +42075,40 @@
         <v>2022</v>
       </c>
       <c r="D463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P463" t="n">
         <v>0</v>
@@ -42126,7 +42126,7 @@
         <v>0</v>
       </c>
       <c r="U463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V463" t="n">
         <v>0</v>
@@ -42144,10 +42144,10 @@
         <v>0</v>
       </c>
       <c r="AA463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB463" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="464">
@@ -42165,40 +42165,40 @@
         <v>2023</v>
       </c>
       <c r="D464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P464" t="n">
         <v>0</v>
@@ -42222,7 +42222,7 @@
         <v>0</v>
       </c>
       <c r="W464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X464" t="n">
         <v>0</v>
@@ -42234,10 +42234,10 @@
         <v>0</v>
       </c>
       <c r="AA464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB464" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="465">
@@ -42255,40 +42255,40 @@
         <v>2024</v>
       </c>
       <c r="D465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P465" t="n">
         <v>0</v>
@@ -42303,7 +42303,7 @@
         <v>0</v>
       </c>
       <c r="T465" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U465" t="n">
         <v>0</v>
@@ -42312,7 +42312,7 @@
         <v>0</v>
       </c>
       <c r="W465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X465" t="n">
         <v>0</v>
@@ -42327,7 +42327,7 @@
         <v>0</v>
       </c>
       <c r="AB465" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="466">
@@ -103905,40 +103905,40 @@
         <v>1996</v>
       </c>
       <c r="D1150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1150" t="n">
         <v>0</v>
@@ -103959,25 +103959,25 @@
         <v>0</v>
       </c>
       <c r="V1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X1150" t="n">
         <v>0</v>
       </c>
       <c r="Y1150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1150" t="n">
         <v>0</v>
       </c>
       <c r="AA1150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB1150" t="n">
-        <v>0</v>
+        <v>0.5404</v>
       </c>
     </row>
     <row r="1151">
@@ -103995,40 +103995,40 @@
         <v>1997</v>
       </c>
       <c r="D1151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1151" t="n">
         <v>0</v>
@@ -104046,28 +104046,28 @@
         <v>0</v>
       </c>
       <c r="U1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W1151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1151" t="n">
         <v>0</v>
       </c>
       <c r="Y1151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z1151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA1151" t="n">
         <v>0</v>
       </c>
       <c r="AB1151" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
     </row>
     <row r="1152">
@@ -104133,7 +104133,7 @@
         <v>0</v>
       </c>
       <c r="T1152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1152" t="n">
         <v>0</v>
@@ -104223,7 +104223,7 @@
         <v>0</v>
       </c>
       <c r="T1153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1153" t="n">
         <v>0</v>
@@ -104265,40 +104265,40 @@
         <v>2000</v>
       </c>
       <c r="D1154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1154" t="n">
         <v>0</v>
@@ -104319,10 +104319,10 @@
         <v>0</v>
       </c>
       <c r="V1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1154" t="n">
         <v>0</v>
@@ -104331,13 +104331,13 @@
         <v>0</v>
       </c>
       <c r="Z1154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA1154" t="n">
         <v>0</v>
       </c>
       <c r="AB1154" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="1155">
@@ -104355,40 +104355,40 @@
         <v>2001</v>
       </c>
       <c r="D1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1155" t="n">
         <v>0</v>
@@ -104403,13 +104403,13 @@
         <v>0</v>
       </c>
       <c r="T1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1155" t="n">
         <v>0</v>
       </c>
       <c r="V1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1155" t="n">
         <v>0</v>
@@ -104418,7 +104418,7 @@
         <v>0</v>
       </c>
       <c r="Y1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1155" t="n">
         <v>0</v>
@@ -104427,7 +104427,7 @@
         <v>0</v>
       </c>
       <c r="AB1155" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1156">
@@ -104445,40 +104445,40 @@
         <v>2002</v>
       </c>
       <c r="D1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1156" t="n">
         <v>0</v>
@@ -104496,7 +104496,7 @@
         <v>0</v>
       </c>
       <c r="U1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V1156" t="n">
         <v>0</v>
@@ -104517,7 +104517,7 @@
         <v>0</v>
       </c>
       <c r="AB1156" t="n">
-        <v>0</v>
+        <v>0.6458</v>
       </c>
     </row>
     <row r="1157">
@@ -104673,7 +104673,7 @@
         <v>0</v>
       </c>
       <c r="T1158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1158" t="n">
         <v>0</v>
@@ -104715,40 +104715,40 @@
         <v>2005</v>
       </c>
       <c r="D1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1159" t="n">
         <v>0</v>
@@ -104763,31 +104763,31 @@
         <v>0</v>
       </c>
       <c r="T1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1159" t="n">
         <v>0</v>
       </c>
       <c r="W1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1159" t="n">
         <v>0</v>
       </c>
       <c r="Y1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1159" t="n">
         <v>0</v>
       </c>
       <c r="AA1159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1159" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="1160">
@@ -104895,40 +104895,40 @@
         <v>2007</v>
       </c>
       <c r="D1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1161" t="n">
         <v>0</v>
@@ -104943,7 +104943,7 @@
         <v>0</v>
       </c>
       <c r="T1161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1161" t="n">
         <v>0</v>
@@ -104952,13 +104952,13 @@
         <v>0</v>
       </c>
       <c r="W1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1161" t="n">
         <v>0</v>
       </c>
       <c r="Y1161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1161" t="n">
         <v>0</v>
@@ -104967,7 +104967,7 @@
         <v>0</v>
       </c>
       <c r="AB1161" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1162">
@@ -105033,7 +105033,7 @@
         <v>0</v>
       </c>
       <c r="T1162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1162" t="n">
         <v>0</v>
@@ -105075,40 +105075,40 @@
         <v>2009</v>
       </c>
       <c r="D1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1163" t="n">
         <v>0</v>
@@ -105126,7 +105126,7 @@
         <v>0</v>
       </c>
       <c r="U1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1163" t="n">
         <v>0</v>
@@ -105138,7 +105138,7 @@
         <v>0</v>
       </c>
       <c r="Y1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1163" t="n">
         <v>0</v>
@@ -105147,7 +105147,7 @@
         <v>0</v>
       </c>
       <c r="AB1163" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1164">
@@ -105165,40 +105165,40 @@
         <v>2010</v>
       </c>
       <c r="D1164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1164" t="n">
         <v>0</v>
@@ -105216,10 +105216,10 @@
         <v>0</v>
       </c>
       <c r="U1164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1164" t="n">
         <v>0</v>
@@ -105228,16 +105228,16 @@
         <v>0</v>
       </c>
       <c r="Y1164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z1164" t="n">
         <v>0</v>
       </c>
       <c r="AA1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1164" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="1165">
@@ -105255,40 +105255,40 @@
         <v>2011</v>
       </c>
       <c r="D1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1165" t="n">
         <v>0</v>
@@ -105303,22 +105303,22 @@
         <v>0</v>
       </c>
       <c r="T1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1165" t="n">
         <v>0</v>
       </c>
       <c r="W1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1165" t="n">
         <v>0</v>
@@ -105327,7 +105327,7 @@
         <v>0</v>
       </c>
       <c r="AB1165" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="1166">
@@ -105345,16 +105345,16 @@
         <v>2012</v>
       </c>
       <c r="D1166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1166" t="n">
         <v>0</v>
@@ -105369,16 +105369,16 @@
         <v>0</v>
       </c>
       <c r="L1166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1166" t="n">
         <v>0</v>
@@ -105393,31 +105393,31 @@
         <v>0</v>
       </c>
       <c r="T1166" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1166" t="n">
         <v>0</v>
       </c>
       <c r="W1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1166" t="n">
         <v>0</v>
       </c>
       <c r="Y1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA1166" t="n">
         <v>0</v>
       </c>
       <c r="AB1166" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="1167">
@@ -105483,7 +105483,7 @@
         <v>0</v>
       </c>
       <c r="T1167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1167" t="n">
         <v>0</v>
@@ -105525,40 +105525,40 @@
         <v>2014</v>
       </c>
       <c r="D1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1168" t="n">
         <v>0</v>
@@ -105573,7 +105573,7 @@
         <v>0</v>
       </c>
       <c r="T1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1168" t="n">
         <v>0</v>
@@ -105582,13 +105582,13 @@
         <v>0</v>
       </c>
       <c r="W1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1168" t="n">
         <v>0</v>
       </c>
       <c r="Y1168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1168" t="n">
         <v>0</v>
@@ -105597,7 +105597,7 @@
         <v>0</v>
       </c>
       <c r="AB1168" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1169">
@@ -105615,40 +105615,40 @@
         <v>2015</v>
       </c>
       <c r="D1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1169" t="n">
         <v>0</v>
@@ -105666,19 +105666,19 @@
         <v>0</v>
       </c>
       <c r="U1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1169" t="n">
         <v>0</v>
       </c>
       <c r="Y1169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z1169" t="n">
         <v>0</v>
@@ -105687,7 +105687,7 @@
         <v>0</v>
       </c>
       <c r="AB1169" t="n">
-        <v>0</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="1170">
@@ -105753,7 +105753,7 @@
         <v>0</v>
       </c>
       <c r="T1170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U1170" t="n">
         <v>0</v>
@@ -105795,40 +105795,40 @@
         <v>2017</v>
       </c>
       <c r="D1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1171" t="n">
         <v>0</v>
@@ -105843,13 +105843,13 @@
         <v>0</v>
       </c>
       <c r="T1171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1171" t="n">
         <v>0</v>
       </c>
       <c r="V1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1171" t="n">
         <v>0</v>
@@ -105867,7 +105867,7 @@
         <v>0</v>
       </c>
       <c r="AB1171" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1172">
@@ -105885,40 +105885,40 @@
         <v>2018</v>
       </c>
       <c r="D1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1172" t="n">
         <v>0</v>
@@ -105933,10 +105933,10 @@
         <v>0</v>
       </c>
       <c r="T1172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1172" t="n">
         <v>0</v>
@@ -105954,10 +105954,10 @@
         <v>0</v>
       </c>
       <c r="AA1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1172" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1173">
@@ -105975,16 +105975,16 @@
         <v>2019</v>
       </c>
       <c r="D1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -105999,16 +105999,16 @@
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1173" t="n">
         <v>0</v>
@@ -106032,7 +106032,7 @@
         <v>0</v>
       </c>
       <c r="W1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1173" t="n">
         <v>0</v>
@@ -106044,10 +106044,10 @@
         <v>0</v>
       </c>
       <c r="AA1173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1173" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="1174">
@@ -106065,40 +106065,40 @@
         <v>2020</v>
       </c>
       <c r="D1174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1174" t="n">
         <v>0</v>
@@ -106116,7 +106116,7 @@
         <v>0</v>
       </c>
       <c r="U1174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V1174" t="n">
         <v>0</v>
@@ -106128,7 +106128,7 @@
         <v>0</v>
       </c>
       <c r="Y1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1174" t="n">
         <v>0</v>
@@ -106137,7 +106137,7 @@
         <v>0</v>
       </c>
       <c r="AB1174" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="1175">
@@ -106155,16 +106155,16 @@
         <v>2021</v>
       </c>
       <c r="D1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -106179,16 +106179,16 @@
         <v>0</v>
       </c>
       <c r="L1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1175" t="n">
         <v>0</v>
@@ -106206,7 +106206,7 @@
         <v>0</v>
       </c>
       <c r="U1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1175" t="n">
         <v>0</v>
@@ -106227,7 +106227,7 @@
         <v>0</v>
       </c>
       <c r="AB1175" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="1176">
@@ -106245,40 +106245,40 @@
         <v>2022</v>
       </c>
       <c r="D1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1176" t="n">
         <v>0</v>
@@ -106296,28 +106296,28 @@
         <v>0</v>
       </c>
       <c r="U1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1176" t="n">
         <v>0</v>
       </c>
       <c r="W1176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X1176" t="n">
         <v>0</v>
       </c>
       <c r="Y1176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z1176" t="n">
         <v>0</v>
       </c>
       <c r="AA1176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1176" t="n">
-        <v>0</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="1177">
@@ -106425,40 +106425,40 @@
         <v>2024</v>
       </c>
       <c r="D1178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1178" t="n">
         <v>0</v>
@@ -106476,10 +106476,10 @@
         <v>0</v>
       </c>
       <c r="U1178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1178" t="n">
         <v>0</v>
@@ -106488,16 +106488,16 @@
         <v>0</v>
       </c>
       <c r="Y1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1178" t="n">
         <v>0</v>
       </c>
       <c r="AA1178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB1178" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="1179">

--- a/Data/output/reforms/output/reform_panel.xlsx
+++ b/Data/output/reforms/output/reform_panel.xlsx
@@ -855,37 +855,37 @@
         <v>1998</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -921,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3535</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="6">
@@ -1047,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6035</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="8">
@@ -1125,37 +1125,37 @@
         <v>2001</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5208</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="9">
@@ -1395,40 +1395,40 @@
         <v>2004</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1446,19 +1446,19 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="12">
@@ -1485,40 +1485,40 @@
         <v>2005</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="13">
@@ -1755,40 +1755,40 @@
         <v>2008</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="16">
@@ -1935,40 +1935,40 @@
         <v>2010</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="18">
@@ -2025,40 +2025,40 @@
         <v>2011</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2082,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="19">
@@ -2115,40 +2115,40 @@
         <v>2012</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2163,31 +2163,31 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="20">
@@ -2205,40 +2205,40 @@
         <v>2013</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="21">
@@ -2577,13 +2577,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -2637,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6365</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="25">
@@ -2655,37 +2655,37 @@
         <v>2018</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.3535</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="26">
@@ -2745,37 +2745,37 @@
         <v>2019</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2802,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6035</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="27">
@@ -2925,13 +2925,13 @@
         <v>2021</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2949,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2976,28 +2976,28 @@
         <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.6931</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="29">
@@ -4995,16 +4995,16 @@
         <v>2013</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -5019,16 +5019,16 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -7065,13 +7065,13 @@
         <v>2005</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -7089,13 +7089,13 @@
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -7119,7 +7119,7 @@
         <v>3</v>
       </c>
       <c r="V74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
@@ -7128,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -7137,7 +7137,7 @@
         <v>2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.6612</v>
+        <v>0.6632</v>
       </c>
     </row>
     <row r="75">
@@ -11745,37 +11745,37 @@
         <v>1995</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
       </c>
       <c r="J126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K126" t="n">
         <v>1</v>
       </c>
       <c r="L126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M126" t="n">
         <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -11796,7 +11796,7 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -11808,7 +11808,7 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z126" t="n">
         <v>0</v>
@@ -11817,7 +11817,7 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0.707</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="127">
@@ -11925,37 +11925,37 @@
         <v>1997</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
@@ -11976,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z128" t="n">
         <v>0</v>
@@ -11997,7 +11997,7 @@
         <v>1</v>
       </c>
       <c r="AB128" t="n">
-        <v>0.3535</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="129">
@@ -12735,13 +12735,13 @@
         <v>2006</v>
       </c>
       <c r="D137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
         <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -12759,13 +12759,13 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
         <v>1</v>
       </c>
       <c r="N137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O137" t="n">
         <v>1</v>
@@ -12786,7 +12786,7 @@
         <v>11</v>
       </c>
       <c r="U137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -12798,16 +12798,16 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0.4803</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="138">
@@ -23175,37 +23175,37 @@
         <v>1998</v>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E253" t="n">
         <v>1</v>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G253" t="n">
         <v>1</v>
       </c>
       <c r="H253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M253" t="n">
         <v>1</v>
       </c>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O253" t="n">
         <v>1</v>
@@ -23232,22 +23232,22 @@
         <v>1</v>
       </c>
       <c r="W253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X253" t="n">
         <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z253" t="n">
         <v>1</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB253" t="n">
-        <v>0.3535</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="254">
@@ -23715,16 +23715,16 @@
         <v>2004</v>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -23739,16 +23739,16 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P259" t="n">
         <v>0</v>
@@ -23769,25 +23769,25 @@
         <v>0</v>
       </c>
       <c r="V259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X259" t="n">
         <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA259" t="n">
         <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>0.4883</v>
       </c>
     </row>
     <row r="260">
@@ -23805,40 +23805,40 @@
         <v>2005</v>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>0</v>
       </c>
       <c r="V260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W260" t="n">
         <v>0</v>
@@ -23868,7 +23868,7 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z260" t="n">
         <v>0</v>
@@ -23877,7 +23877,7 @@
         <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="261">
@@ -23895,16 +23895,16 @@
         <v>2006</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -23919,16 +23919,16 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P261" t="n">
         <v>0</v>
@@ -23943,10 +23943,10 @@
         <v>0</v>
       </c>
       <c r="T261" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V261" t="n">
         <v>0</v>
@@ -23958,7 +23958,7 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z261" t="n">
         <v>0</v>
@@ -23967,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="262">
@@ -23985,40 +23985,40 @@
         <v>2007</v>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P262" t="n">
         <v>0</v>
@@ -24042,13 +24042,13 @@
         <v>0</v>
       </c>
       <c r="W262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X262" t="n">
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z262" t="n">
         <v>0</v>
@@ -24057,7 +24057,7 @@
         <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="263">
@@ -24075,16 +24075,16 @@
         <v>2008</v>
       </c>
       <c r="D263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -24099,16 +24099,16 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P263" t="n">
         <v>0</v>
@@ -24123,10 +24123,10 @@
         <v>0</v>
       </c>
       <c r="T263" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V263" t="n">
         <v>0</v>
@@ -24144,10 +24144,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="264">
@@ -24165,40 +24165,40 @@
         <v>2009</v>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P264" t="n">
         <v>0</v>
@@ -24216,7 +24216,7 @@
         <v>0</v>
       </c>
       <c r="U264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V264" t="n">
         <v>0</v>
@@ -24228,16 +24228,16 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z264" t="n">
         <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB264" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="265">
@@ -24303,7 +24303,7 @@
         <v>0</v>
       </c>
       <c r="T265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U265" t="n">
         <v>0</v>
@@ -24615,40 +24615,40 @@
         <v>2014</v>
       </c>
       <c r="D269" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P269" t="n">
         <v>0</v>
@@ -24663,31 +24663,31 @@
         <v>0</v>
       </c>
       <c r="T269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X269" t="n">
         <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB269" t="n">
-        <v>0</v>
+        <v>0.6618000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -24795,40 +24795,40 @@
         <v>2016</v>
       </c>
       <c r="D271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P271" t="n">
         <v>0</v>
@@ -24843,16 +24843,16 @@
         <v>0</v>
       </c>
       <c r="T271" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V271" t="n">
         <v>0</v>
       </c>
       <c r="W271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X271" t="n">
         <v>0</v>
@@ -24861,13 +24861,13 @@
         <v>0</v>
       </c>
       <c r="Z271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
       </c>
       <c r="AB271" t="n">
-        <v>0</v>
+        <v>0.5208</v>
       </c>
     </row>
     <row r="272">
@@ -24975,40 +24975,40 @@
         <v>2018</v>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P273" t="n">
         <v>0</v>
@@ -25026,28 +25026,28 @@
         <v>0</v>
       </c>
       <c r="U273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V273" t="n">
         <v>0</v>
       </c>
       <c r="W273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X273" t="n">
         <v>0</v>
       </c>
       <c r="Y273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA273" t="n">
         <v>0</v>
       </c>
       <c r="AB273" t="n">
-        <v>0</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="274">
@@ -25113,16 +25113,16 @@
         <v>0</v>
       </c>
       <c r="T274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U274" t="n">
         <v>0</v>
       </c>
       <c r="V274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X274" t="n">
         <v>0</v>
@@ -25155,16 +25155,16 @@
         <v>2020</v>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -25179,16 +25179,16 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P275" t="n">
         <v>0</v>
@@ -25203,13 +25203,13 @@
         <v>0</v>
       </c>
       <c r="T275" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U275" t="n">
         <v>0</v>
       </c>
       <c r="V275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W275" t="n">
         <v>0</v>
@@ -25218,7 +25218,7 @@
         <v>0</v>
       </c>
       <c r="Y275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z275" t="n">
         <v>0</v>
@@ -25227,7 +25227,7 @@
         <v>0</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="276">
@@ -31365,40 +31365,40 @@
         <v>1996</v>
       </c>
       <c r="D344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P344" t="n">
         <v>0</v>
@@ -31416,7 +31416,7 @@
         <v>0</v>
       </c>
       <c r="U344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V344" t="n">
         <v>0</v>
@@ -31437,7 +31437,7 @@
         <v>0</v>
       </c>
       <c r="AB344" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="345">
@@ -31455,40 +31455,40 @@
         <v>1997</v>
       </c>
       <c r="D345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P345" t="n">
         <v>0</v>
@@ -31506,7 +31506,7 @@
         <v>0</v>
       </c>
       <c r="U345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V345" t="n">
         <v>0</v>
@@ -31518,7 +31518,7 @@
         <v>0</v>
       </c>
       <c r="Y345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z345" t="n">
         <v>0</v>
@@ -31527,7 +31527,7 @@
         <v>0</v>
       </c>
       <c r="AB345" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="346">
@@ -31545,37 +31545,37 @@
         <v>1998</v>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E346" t="n">
         <v>1</v>
       </c>
       <c r="F346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G346" t="n">
         <v>1</v>
       </c>
       <c r="H346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M346" t="n">
         <v>1</v>
       </c>
       <c r="N346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O346" t="n">
         <v>1</v>
@@ -31593,10 +31593,10 @@
         <v>0</v>
       </c>
       <c r="T346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V346" t="n">
         <v>1</v>
@@ -31608,7 +31608,7 @@
         <v>0</v>
       </c>
       <c r="Y346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z346" t="n">
         <v>1</v>
@@ -31617,7 +31617,7 @@
         <v>0</v>
       </c>
       <c r="AB346" t="n">
-        <v>0.3535</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="347">
@@ -31725,16 +31725,16 @@
         <v>2000</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -31749,16 +31749,16 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P348" t="n">
         <v>0</v>
@@ -31779,7 +31779,7 @@
         <v>0</v>
       </c>
       <c r="V348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W348" t="n">
         <v>0</v>
@@ -31788,7 +31788,7 @@
         <v>0</v>
       </c>
       <c r="Y348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z348" t="n">
         <v>0</v>
@@ -31797,7 +31797,7 @@
         <v>0</v>
       </c>
       <c r="AB348" t="n">
-        <v>0.3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -31815,37 +31815,37 @@
         <v>2001</v>
       </c>
       <c r="D349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E349" t="n">
         <v>1</v>
       </c>
       <c r="F349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G349" t="n">
         <v>1</v>
       </c>
       <c r="H349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M349" t="n">
         <v>1</v>
       </c>
       <c r="N349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O349" t="n">
         <v>1</v>
@@ -31866,7 +31866,7 @@
         <v>0</v>
       </c>
       <c r="U349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V349" t="n">
         <v>1</v>
@@ -31878,7 +31878,7 @@
         <v>0</v>
       </c>
       <c r="Y349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z349" t="n">
         <v>0</v>
@@ -31887,7 +31887,7 @@
         <v>0</v>
       </c>
       <c r="AB349" t="n">
-        <v>0.552</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="350">
@@ -31995,37 +31995,37 @@
         <v>2003</v>
       </c>
       <c r="D351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E351" t="n">
         <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G351" t="n">
         <v>1</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M351" t="n">
         <v>1</v>
       </c>
       <c r="N351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O351" t="n">
         <v>1</v>
@@ -32046,7 +32046,7 @@
         <v>2</v>
       </c>
       <c r="U351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V351" t="n">
         <v>1</v>
@@ -32067,7 +32067,7 @@
         <v>0</v>
       </c>
       <c r="AB351" t="n">
-        <v>0.5404</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="352">
@@ -32355,37 +32355,37 @@
         <v>2007</v>
       </c>
       <c r="D355" t="n">
+        <v>4</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1</v>
+      </c>
+      <c r="F355" t="n">
+        <v>4</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1</v>
+      </c>
+      <c r="H355" t="n">
         <v>3</v>
       </c>
-      <c r="E355" t="n">
-        <v>1</v>
-      </c>
-      <c r="F355" t="n">
+      <c r="I355" t="n">
+        <v>1</v>
+      </c>
+      <c r="J355" t="n">
         <v>3</v>
       </c>
-      <c r="G355" t="n">
-        <v>1</v>
-      </c>
-      <c r="H355" t="n">
-        <v>2</v>
-      </c>
-      <c r="I355" t="n">
-        <v>1</v>
-      </c>
-      <c r="J355" t="n">
-        <v>2</v>
-      </c>
       <c r="K355" t="n">
         <v>1</v>
       </c>
       <c r="L355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M355" t="n">
         <v>1</v>
       </c>
       <c r="N355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O355" t="n">
         <v>1</v>
@@ -32406,7 +32406,7 @@
         <v>14</v>
       </c>
       <c r="U355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V355" t="n">
         <v>1</v>
@@ -32418,7 +32418,7 @@
         <v>1</v>
       </c>
       <c r="Y355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z355" t="n">
         <v>0</v>
@@ -32427,7 +32427,7 @@
         <v>1</v>
       </c>
       <c r="AB355" t="n">
-        <v>0.6237</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="356">
@@ -32445,16 +32445,16 @@
         <v>2008</v>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -32469,16 +32469,16 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P356" t="n">
         <v>0</v>
@@ -32493,16 +32493,16 @@
         <v>0</v>
       </c>
       <c r="T356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U356" t="n">
         <v>0</v>
       </c>
       <c r="V356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X356" t="n">
         <v>0</v>
@@ -32514,10 +32514,10 @@
         <v>0</v>
       </c>
       <c r="AA356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB356" t="n">
-        <v>0</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="357">
@@ -32715,40 +32715,40 @@
         <v>2011</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P359" t="n">
         <v>0</v>
@@ -32772,13 +32772,13 @@
         <v>0</v>
       </c>
       <c r="W359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X359" t="n">
         <v>0</v>
       </c>
       <c r="Y359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z359" t="n">
         <v>0</v>
@@ -32787,7 +32787,7 @@
         <v>0</v>
       </c>
       <c r="AB359" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="360">
@@ -32805,40 +32805,40 @@
         <v>2012</v>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P360" t="n">
         <v>0</v>
@@ -32853,16 +32853,16 @@
         <v>0</v>
       </c>
       <c r="T360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U360" t="n">
         <v>0</v>
       </c>
       <c r="V360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X360" t="n">
         <v>0</v>
@@ -32871,13 +32871,13 @@
         <v>0</v>
       </c>
       <c r="Z360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB360" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="361">
@@ -32895,40 +32895,40 @@
         <v>2013</v>
       </c>
       <c r="D361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P361" t="n">
         <v>0</v>
@@ -32946,7 +32946,7 @@
         <v>0</v>
       </c>
       <c r="U361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V361" t="n">
         <v>0</v>
@@ -32967,7 +32967,7 @@
         <v>0</v>
       </c>
       <c r="AB361" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="362">
@@ -32985,40 +32985,40 @@
         <v>2014</v>
       </c>
       <c r="D362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P362" t="n">
         <v>0</v>
@@ -33033,31 +33033,31 @@
         <v>0</v>
       </c>
       <c r="T362" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W362" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X362" t="n">
         <v>0</v>
       </c>
       <c r="Y362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z362" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB362" t="n">
-        <v>0</v>
+        <v>0.7493</v>
       </c>
     </row>
     <row r="363">
@@ -33213,7 +33213,7 @@
         <v>0</v>
       </c>
       <c r="T364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U364" t="n">
         <v>0</v>
@@ -33345,37 +33345,37 @@
         <v>2018</v>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E366" t="n">
         <v>1</v>
       </c>
       <c r="F366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G366" t="n">
         <v>1</v>
       </c>
       <c r="H366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M366" t="n">
         <v>1</v>
       </c>
       <c r="N366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O366" t="n">
         <v>1</v>
@@ -33396,28 +33396,28 @@
         <v>0</v>
       </c>
       <c r="U366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V366" t="n">
         <v>0</v>
       </c>
       <c r="W366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X366" t="n">
         <v>0</v>
       </c>
       <c r="Y366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z366" t="n">
         <v>1</v>
       </c>
       <c r="AA366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.3535</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="367">
@@ -33435,16 +33435,16 @@
         <v>2019</v>
       </c>
       <c r="D367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -33459,16 +33459,16 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P367" t="n">
         <v>0</v>
@@ -33483,7 +33483,7 @@
         <v>0</v>
       </c>
       <c r="T367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U367" t="n">
         <v>0</v>
@@ -33492,13 +33492,13 @@
         <v>0</v>
       </c>
       <c r="W367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X367" t="n">
         <v>0</v>
       </c>
       <c r="Y367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z367" t="n">
         <v>0</v>
@@ -33507,7 +33507,7 @@
         <v>0</v>
       </c>
       <c r="AB367" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="368">
@@ -33525,37 +33525,37 @@
         <v>2020</v>
       </c>
       <c r="D368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E368" t="n">
         <v>1</v>
       </c>
       <c r="F368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G368" t="n">
         <v>1</v>
       </c>
       <c r="H368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I368" t="n">
         <v>1</v>
       </c>
       <c r="J368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K368" t="n">
         <v>1</v>
       </c>
       <c r="L368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M368" t="n">
         <v>1</v>
       </c>
       <c r="N368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O368" t="n">
         <v>1</v>
@@ -33582,13 +33582,13 @@
         <v>0</v>
       </c>
       <c r="W368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X368" t="n">
         <v>0</v>
       </c>
       <c r="Y368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z368" t="n">
         <v>0</v>
@@ -33597,7 +33597,7 @@
         <v>1</v>
       </c>
       <c r="AB368" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="369">
@@ -33885,40 +33885,40 @@
         <v>2024</v>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P372" t="n">
         <v>0</v>
@@ -33942,7 +33942,7 @@
         <v>0</v>
       </c>
       <c r="W372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X372" t="n">
         <v>0</v>
@@ -33954,10 +33954,10 @@
         <v>0</v>
       </c>
       <c r="AA372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB372" t="n">
-        <v>0.6035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -36057,16 +36057,16 @@
         <v>1</v>
       </c>
       <c r="H396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L396" t="n">
         <v>5</v>
@@ -36117,7 +36117,7 @@
         <v>1</v>
       </c>
       <c r="AB396" t="n">
-        <v>0.6118</v>
+        <v>0.5618</v>
       </c>
     </row>
     <row r="397">
@@ -36288,13 +36288,13 @@
         <v>0</v>
       </c>
       <c r="Y398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z398" t="n">
         <v>0</v>
       </c>
       <c r="AA398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB398" t="n">
         <v>0.699</v>
@@ -36327,16 +36327,16 @@
         <v>1</v>
       </c>
       <c r="H399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L399" t="n">
         <v>2</v>
@@ -36366,10 +36366,10 @@
         <v>0</v>
       </c>
       <c r="U399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W399" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1</v>
       </c>
       <c r="AB399" t="n">
-        <v>0.427</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="400">
@@ -36405,37 +36405,37 @@
         <v>2021</v>
       </c>
       <c r="D400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E400" t="n">
         <v>1</v>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G400" t="n">
         <v>1</v>
       </c>
       <c r="H400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M400" t="n">
         <v>1</v>
       </c>
       <c r="N400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O400" t="n">
         <v>1</v>
@@ -36456,7 +36456,7 @@
         <v>0</v>
       </c>
       <c r="U400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V400" t="n">
         <v>0</v>
@@ -36468,7 +36468,7 @@
         <v>0</v>
       </c>
       <c r="Y400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z400" t="n">
         <v>0</v>
@@ -36477,7 +36477,7 @@
         <v>0</v>
       </c>
       <c r="AB400" t="n">
-        <v>0.552</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="401">
@@ -36495,13 +36495,13 @@
         <v>2022</v>
       </c>
       <c r="D401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E401" t="n">
         <v>1</v>
       </c>
       <c r="F401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G401" t="n">
         <v>1</v>
@@ -36519,13 +36519,13 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M401" t="n">
         <v>1</v>
       </c>
       <c r="N401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O401" t="n">
         <v>1</v>
@@ -36552,7 +36552,7 @@
         <v>0</v>
       </c>
       <c r="W401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X401" t="n">
         <v>0</v>
@@ -36561,13 +36561,13 @@
         <v>2</v>
       </c>
       <c r="Z401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA401" t="n">
         <v>0</v>
       </c>
       <c r="AB401" t="n">
-        <v>0.4883</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="402">
@@ -41625,40 +41625,40 @@
         <v>2017</v>
       </c>
       <c r="D458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P458" t="n">
         <v>0</v>
@@ -41676,7 +41676,7 @@
         <v>0</v>
       </c>
       <c r="U458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V458" t="n">
         <v>0</v>
@@ -41688,7 +41688,7 @@
         <v>0</v>
       </c>
       <c r="Y458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z458" t="n">
         <v>0</v>
@@ -41697,7 +41697,7 @@
         <v>0</v>
       </c>
       <c r="AB458" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="459">
@@ -41727,13 +41727,13 @@
         <v>1</v>
       </c>
       <c r="H459" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I459" t="n">
         <v>1</v>
       </c>
       <c r="J459" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K459" t="n">
         <v>1</v>
@@ -41787,7 +41787,7 @@
         <v>0</v>
       </c>
       <c r="AB459" t="n">
-        <v>0.7806</v>
+        <v>0.6993</v>
       </c>
     </row>
     <row r="460">
@@ -41805,16 +41805,16 @@
         <v>2019</v>
       </c>
       <c r="D460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -41829,16 +41829,16 @@
         <v>0</v>
       </c>
       <c r="L460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P460" t="n">
         <v>0</v>
@@ -41856,7 +41856,7 @@
         <v>7</v>
       </c>
       <c r="U460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V460" t="n">
         <v>0</v>
@@ -41874,10 +41874,10 @@
         <v>0</v>
       </c>
       <c r="AA460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB460" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="461">
@@ -50997,16 +50997,16 @@
         <v>1</v>
       </c>
       <c r="H562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L562" t="n">
         <v>1</v>
@@ -51057,7 +51057,7 @@
         <v>0</v>
       </c>
       <c r="AB562" t="n">
-        <v>0.6035</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="563">
@@ -51075,37 +51075,37 @@
         <v>1998</v>
       </c>
       <c r="D563" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E563" t="n">
         <v>1</v>
       </c>
       <c r="F563" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G563" t="n">
         <v>1</v>
       </c>
       <c r="H563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I563" t="n">
         <v>1</v>
       </c>
       <c r="J563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K563" t="n">
         <v>1</v>
       </c>
       <c r="L563" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M563" t="n">
         <v>1</v>
       </c>
       <c r="N563" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O563" t="n">
         <v>1</v>
@@ -51126,28 +51126,28 @@
         <v>0</v>
       </c>
       <c r="U563" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V563" t="n">
         <v>1</v>
       </c>
       <c r="W563" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X563" t="n">
         <v>0</v>
       </c>
       <c r="Y563" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z563" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA563" t="n">
         <v>1</v>
       </c>
       <c r="AB563" t="n">
-        <v>0.677</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="564">
@@ -51177,16 +51177,16 @@
         <v>1</v>
       </c>
       <c r="H564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L564" t="n">
         <v>1</v>
@@ -51237,7 +51237,7 @@
         <v>0</v>
       </c>
       <c r="AB564" t="n">
-        <v>0.6035</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="565">
@@ -51255,37 +51255,37 @@
         <v>2000</v>
       </c>
       <c r="D565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E565" t="n">
         <v>1</v>
       </c>
       <c r="F565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G565" t="n">
         <v>1</v>
       </c>
       <c r="H565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I565" t="n">
         <v>1</v>
       </c>
       <c r="J565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K565" t="n">
         <v>1</v>
       </c>
       <c r="L565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M565" t="n">
         <v>1</v>
       </c>
       <c r="N565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O565" t="n">
         <v>1</v>
@@ -51306,7 +51306,7 @@
         <v>0</v>
       </c>
       <c r="U565" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V565" t="n">
         <v>0</v>
@@ -51318,16 +51318,16 @@
         <v>0</v>
       </c>
       <c r="Y565" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z565" t="n">
         <v>0</v>
       </c>
       <c r="AA565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB565" t="n">
-        <v>0.6035</v>
+        <v>0.7383</v>
       </c>
     </row>
     <row r="566">
@@ -51345,40 +51345,40 @@
         <v>2001</v>
       </c>
       <c r="D566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P566" t="n">
         <v>0</v>
@@ -51402,7 +51402,7 @@
         <v>0</v>
       </c>
       <c r="W566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X566" t="n">
         <v>0</v>
@@ -51414,10 +51414,10 @@
         <v>0</v>
       </c>
       <c r="AA566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB566" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="567">
@@ -58917,13 +58917,13 @@
         <v>1</v>
       </c>
       <c r="H650" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I650" t="n">
         <v>1</v>
       </c>
       <c r="J650" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K650" t="n">
         <v>1</v>
@@ -58977,7 +58977,7 @@
         <v>1</v>
       </c>
       <c r="AB650" t="n">
-        <v>0.7618</v>
+        <v>0.7118</v>
       </c>
     </row>
     <row r="651">
@@ -58995,40 +58995,40 @@
         <v>2024</v>
       </c>
       <c r="D651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P651" t="n">
         <v>0</v>
@@ -59052,13 +59052,13 @@
         <v>0</v>
       </c>
       <c r="W651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X651" t="n">
         <v>0</v>
       </c>
       <c r="Y651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z651" t="n">
         <v>0</v>
@@ -59067,7 +59067,7 @@
         <v>0</v>
       </c>
       <c r="AB651" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="652">
@@ -59175,13 +59175,13 @@
         <v>1995</v>
       </c>
       <c r="D653" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E653" t="n">
         <v>1</v>
       </c>
       <c r="F653" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G653" t="n">
         <v>1</v>
@@ -59211,16 +59211,16 @@
         <v>1</v>
       </c>
       <c r="P653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T653" t="n">
         <v>0</v>
@@ -59229,7 +59229,7 @@
         <v>1</v>
       </c>
       <c r="V653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W653" t="n">
         <v>0</v>
@@ -59241,13 +59241,13 @@
         <v>1</v>
       </c>
       <c r="Z653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA653" t="n">
         <v>0</v>
       </c>
       <c r="AB653" t="n">
-        <v>0.302</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="654">
@@ -59355,13 +59355,13 @@
         <v>1997</v>
       </c>
       <c r="D655" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E655" t="n">
         <v>1</v>
       </c>
       <c r="F655" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G655" t="n">
         <v>1</v>
@@ -59379,13 +59379,13 @@
         <v>1</v>
       </c>
       <c r="L655" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M655" t="n">
         <v>1</v>
       </c>
       <c r="N655" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O655" t="n">
         <v>1</v>
@@ -59412,13 +59412,13 @@
         <v>1</v>
       </c>
       <c r="W655" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X655" t="n">
         <v>0</v>
       </c>
       <c r="Y655" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z655" t="n">
         <v>0</v>
@@ -59427,7 +59427,7 @@
         <v>0</v>
       </c>
       <c r="AB655" t="n">
-        <v>0.552</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="656">
@@ -61965,40 +61965,40 @@
         <v>1995</v>
       </c>
       <c r="D684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P684" t="n">
         <v>0</v>
@@ -62016,7 +62016,7 @@
         <v>0</v>
       </c>
       <c r="U684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V684" t="n">
         <v>0</v>
@@ -62028,7 +62028,7 @@
         <v>0</v>
       </c>
       <c r="Y684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z684" t="n">
         <v>0</v>
@@ -62037,7 +62037,7 @@
         <v>0</v>
       </c>
       <c r="AB684" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="685">
@@ -62055,40 +62055,40 @@
         <v>1996</v>
       </c>
       <c r="D685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P685" t="n">
         <v>0</v>
@@ -62103,10 +62103,10 @@
         <v>0</v>
       </c>
       <c r="T685" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V685" t="n">
         <v>0</v>
@@ -62115,7 +62115,7 @@
         <v>0</v>
       </c>
       <c r="X685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y685" t="n">
         <v>0</v>
@@ -62127,7 +62127,7 @@
         <v>0</v>
       </c>
       <c r="AB685" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="686">
@@ -62145,40 +62145,40 @@
         <v>1997</v>
       </c>
       <c r="D686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P686" t="n">
         <v>0</v>
@@ -62202,13 +62202,13 @@
         <v>0</v>
       </c>
       <c r="W686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X686" t="n">
         <v>0</v>
       </c>
       <c r="Y686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z686" t="n">
         <v>0</v>
@@ -62217,7 +62217,7 @@
         <v>0</v>
       </c>
       <c r="AB686" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="687">
@@ -62235,40 +62235,40 @@
         <v>1998</v>
       </c>
       <c r="D687" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F687" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H687" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J687" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N687" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P687" t="n">
         <v>0</v>
@@ -62283,16 +62283,16 @@
         <v>0</v>
       </c>
       <c r="T687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X687" t="n">
         <v>0</v>
@@ -62301,13 +62301,13 @@
         <v>0</v>
       </c>
       <c r="Z687" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB687" t="n">
-        <v>0</v>
+        <v>0.6677999999999999</v>
       </c>
     </row>
     <row r="688">
@@ -62325,37 +62325,37 @@
         <v>1999</v>
       </c>
       <c r="D688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E688" t="n">
         <v>1</v>
       </c>
       <c r="F688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G688" t="n">
         <v>1</v>
       </c>
       <c r="H688" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I688" t="n">
         <v>1</v>
       </c>
       <c r="J688" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K688" t="n">
         <v>1</v>
       </c>
       <c r="L688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M688" t="n">
         <v>1</v>
       </c>
       <c r="N688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O688" t="n">
         <v>1</v>
@@ -62373,7 +62373,7 @@
         <v>0</v>
       </c>
       <c r="T688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U688" t="n">
         <v>0</v>
@@ -62382,13 +62382,13 @@
         <v>1</v>
       </c>
       <c r="W688" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X688" t="n">
         <v>0</v>
       </c>
       <c r="Y688" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z688" t="n">
         <v>1</v>
@@ -62397,7 +62397,7 @@
         <v>1</v>
       </c>
       <c r="AB688" t="n">
-        <v>0.6549</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="689">
@@ -62415,40 +62415,40 @@
         <v>2000</v>
       </c>
       <c r="D689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P689" t="n">
         <v>0</v>
@@ -62463,10 +62463,10 @@
         <v>0</v>
       </c>
       <c r="T689" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V689" t="n">
         <v>0</v>
@@ -62475,7 +62475,7 @@
         <v>0</v>
       </c>
       <c r="X689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y689" t="n">
         <v>0</v>
@@ -62487,7 +62487,7 @@
         <v>0</v>
       </c>
       <c r="AB689" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="690">
@@ -62511,58 +62511,58 @@
         <v>1</v>
       </c>
       <c r="F690" t="n">
+        <v>2</v>
+      </c>
+      <c r="G690" t="n">
+        <v>1</v>
+      </c>
+      <c r="H690" t="n">
         <v>3</v>
       </c>
-      <c r="G690" t="n">
-        <v>1</v>
-      </c>
-      <c r="H690" t="n">
-        <v>2</v>
-      </c>
       <c r="I690" t="n">
         <v>1</v>
       </c>
       <c r="J690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K690" t="n">
         <v>1</v>
       </c>
       <c r="L690" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M690" t="n">
         <v>1</v>
       </c>
       <c r="N690" t="n">
+        <v>2</v>
+      </c>
+      <c r="O690" t="n">
+        <v>1</v>
+      </c>
+      <c r="P690" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q690" t="n">
+        <v>0</v>
+      </c>
+      <c r="R690" t="n">
+        <v>0</v>
+      </c>
+      <c r="S690" t="n">
+        <v>0</v>
+      </c>
+      <c r="T690" t="n">
         <v>3</v>
       </c>
-      <c r="O690" t="n">
-        <v>1</v>
-      </c>
-      <c r="P690" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q690" t="n">
-        <v>0</v>
-      </c>
-      <c r="R690" t="n">
-        <v>0</v>
-      </c>
-      <c r="S690" t="n">
-        <v>0</v>
-      </c>
-      <c r="T690" t="n">
-        <v>2</v>
-      </c>
       <c r="U690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V690" t="n">
         <v>2</v>
       </c>
       <c r="W690" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X690" t="n">
         <v>1</v>
@@ -62571,13 +62571,13 @@
         <v>0</v>
       </c>
       <c r="Z690" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA690" t="n">
         <v>0</v>
       </c>
       <c r="AB690" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="691">
@@ -62595,40 +62595,40 @@
         <v>2002</v>
       </c>
       <c r="D691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P691" t="n">
         <v>0</v>
@@ -62649,7 +62649,7 @@
         <v>0</v>
       </c>
       <c r="V691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W691" t="n">
         <v>0</v>
@@ -62658,7 +62658,7 @@
         <v>0</v>
       </c>
       <c r="Y691" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z691" t="n">
         <v>0</v>
@@ -62667,7 +62667,7 @@
         <v>0</v>
       </c>
       <c r="AB691" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="692">
@@ -62685,37 +62685,37 @@
         <v>2003</v>
       </c>
       <c r="D692" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E692" t="n">
         <v>1</v>
       </c>
       <c r="F692" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G692" t="n">
         <v>1</v>
       </c>
       <c r="H692" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I692" t="n">
         <v>1</v>
       </c>
       <c r="J692" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K692" t="n">
         <v>1</v>
       </c>
       <c r="L692" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M692" t="n">
         <v>1</v>
       </c>
       <c r="N692" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O692" t="n">
         <v>1</v>
@@ -62733,10 +62733,10 @@
         <v>0</v>
       </c>
       <c r="T692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U692" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V692" t="n">
         <v>2</v>
@@ -62745,19 +62745,19 @@
         <v>1</v>
       </c>
       <c r="X692" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y692" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z692" t="n">
         <v>1</v>
       </c>
       <c r="AA692" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB692" t="n">
-        <v>0.574</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="693">
@@ -62826,13 +62826,13 @@
         <v>0</v>
       </c>
       <c r="U693" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V693" t="n">
         <v>0</v>
       </c>
       <c r="W693" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X693" t="n">
         <v>0</v>
@@ -62841,10 +62841,10 @@
         <v>0</v>
       </c>
       <c r="Z693" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA693" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB693" t="n">
         <v>0.6035</v>
@@ -62955,13 +62955,13 @@
         <v>2006</v>
       </c>
       <c r="D695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E695" t="n">
         <v>1</v>
       </c>
       <c r="F695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G695" t="n">
         <v>1</v>
@@ -62979,13 +62979,13 @@
         <v>1</v>
       </c>
       <c r="L695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M695" t="n">
         <v>1</v>
       </c>
       <c r="N695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O695" t="n">
         <v>1</v>
@@ -63003,31 +63003,31 @@
         <v>0</v>
       </c>
       <c r="T695" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U695" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V695" t="n">
         <v>0</v>
       </c>
       <c r="W695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X695" t="n">
         <v>0</v>
       </c>
       <c r="Y695" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA695" t="n">
         <v>0</v>
       </c>
       <c r="AB695" t="n">
-        <v>0.6035</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="696">
@@ -63045,13 +63045,13 @@
         <v>2007</v>
       </c>
       <c r="D696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E696" t="n">
         <v>1</v>
       </c>
       <c r="F696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G696" t="n">
         <v>1</v>
@@ -63069,13 +63069,13 @@
         <v>0</v>
       </c>
       <c r="L696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M696" t="n">
         <v>1</v>
       </c>
       <c r="N696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O696" t="n">
         <v>1</v>
@@ -63096,7 +63096,7 @@
         <v>0</v>
       </c>
       <c r="U696" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V696" t="n">
         <v>0</v>
@@ -63117,7 +63117,7 @@
         <v>0</v>
       </c>
       <c r="AB696" t="n">
-        <v>0.427</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="697">
@@ -63315,13 +63315,13 @@
         <v>2010</v>
       </c>
       <c r="D699" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E699" t="n">
         <v>1</v>
       </c>
       <c r="F699" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G699" t="n">
         <v>1</v>
@@ -63339,13 +63339,13 @@
         <v>1</v>
       </c>
       <c r="L699" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M699" t="n">
         <v>1</v>
       </c>
       <c r="N699" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O699" t="n">
         <v>1</v>
@@ -63372,10 +63372,10 @@
         <v>0</v>
       </c>
       <c r="W699" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X699" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y699" t="n">
         <v>1</v>
@@ -63387,7 +63387,7 @@
         <v>0</v>
       </c>
       <c r="AB699" t="n">
-        <v>0.5208</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="700">
@@ -63495,37 +63495,37 @@
         <v>2012</v>
       </c>
       <c r="D701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E701" t="n">
         <v>1</v>
       </c>
       <c r="F701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G701" t="n">
         <v>1</v>
       </c>
       <c r="H701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I701" t="n">
         <v>1</v>
       </c>
       <c r="J701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K701" t="n">
         <v>1</v>
       </c>
       <c r="L701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M701" t="n">
         <v>1</v>
       </c>
       <c r="N701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O701" t="n">
         <v>1</v>
@@ -63552,13 +63552,13 @@
         <v>0</v>
       </c>
       <c r="W701" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X701" t="n">
         <v>1</v>
       </c>
       <c r="Y701" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z701" t="n">
         <v>0</v>
@@ -63567,7 +63567,7 @@
         <v>0</v>
       </c>
       <c r="AB701" t="n">
-        <v>0.677</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="702">
@@ -63585,37 +63585,37 @@
         <v>2013</v>
       </c>
       <c r="D702" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E702" t="n">
         <v>1</v>
       </c>
       <c r="F702" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G702" t="n">
         <v>1</v>
       </c>
       <c r="H702" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I702" t="n">
         <v>1</v>
       </c>
       <c r="J702" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K702" t="n">
         <v>1</v>
       </c>
       <c r="L702" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M702" t="n">
         <v>1</v>
       </c>
       <c r="N702" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O702" t="n">
         <v>1</v>
@@ -63633,7 +63633,7 @@
         <v>0</v>
       </c>
       <c r="T702" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U702" t="n">
         <v>1</v>
@@ -63642,13 +63642,13 @@
         <v>0</v>
       </c>
       <c r="W702" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X702" t="n">
         <v>0</v>
       </c>
       <c r="Y702" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z702" t="n">
         <v>0</v>
@@ -63657,7 +63657,7 @@
         <v>0</v>
       </c>
       <c r="AB702" t="n">
-        <v>0.6237</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="703">
@@ -63687,16 +63687,16 @@
         <v>1</v>
       </c>
       <c r="H703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L703" t="n">
         <v>1</v>
@@ -63726,10 +63726,10 @@
         <v>0</v>
       </c>
       <c r="U703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W703" t="n">
         <v>0</v>
@@ -63738,16 +63738,16 @@
         <v>0</v>
       </c>
       <c r="Y703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA703" t="n">
         <v>0</v>
       </c>
       <c r="AB703" t="n">
-        <v>0.6035</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="704">
@@ -63765,37 +63765,37 @@
         <v>2015</v>
       </c>
       <c r="D704" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E704" t="n">
         <v>1</v>
       </c>
       <c r="F704" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G704" t="n">
         <v>1</v>
       </c>
       <c r="H704" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I704" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J704" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K704" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L704" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M704" t="n">
         <v>1</v>
       </c>
       <c r="N704" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O704" t="n">
         <v>1</v>
@@ -63822,22 +63822,22 @@
         <v>0</v>
       </c>
       <c r="W704" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X704" t="n">
         <v>0</v>
       </c>
       <c r="Y704" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z704" t="n">
         <v>1</v>
       </c>
       <c r="AA704" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB704" t="n">
-        <v>0.6237</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="705">
@@ -63855,13 +63855,13 @@
         <v>2016</v>
       </c>
       <c r="D705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E705" t="n">
         <v>1</v>
       </c>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G705" t="n">
         <v>1</v>
@@ -63879,13 +63879,13 @@
         <v>1</v>
       </c>
       <c r="L705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M705" t="n">
         <v>1</v>
       </c>
       <c r="N705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O705" t="n">
         <v>1</v>
@@ -63906,7 +63906,7 @@
         <v>0</v>
       </c>
       <c r="U705" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V705" t="n">
         <v>1</v>
@@ -63921,13 +63921,13 @@
         <v>1</v>
       </c>
       <c r="Z705" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA705" t="n">
         <v>1</v>
       </c>
       <c r="AB705" t="n">
-        <v>0.7383</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="706">
@@ -63945,40 +63945,40 @@
         <v>2017</v>
       </c>
       <c r="D706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P706" t="n">
         <v>0</v>
@@ -64002,7 +64002,7 @@
         <v>0</v>
       </c>
       <c r="W706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X706" t="n">
         <v>0</v>
@@ -64014,10 +64014,10 @@
         <v>0</v>
       </c>
       <c r="AA706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB706" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="707">
@@ -64035,13 +64035,13 @@
         <v>2018</v>
       </c>
       <c r="D707" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E707" t="n">
         <v>1</v>
       </c>
       <c r="F707" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G707" t="n">
         <v>1</v>
@@ -64059,13 +64059,13 @@
         <v>1</v>
       </c>
       <c r="L707" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M707" t="n">
         <v>1</v>
       </c>
       <c r="N707" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O707" t="n">
         <v>1</v>
@@ -64089,7 +64089,7 @@
         <v>1</v>
       </c>
       <c r="V707" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W707" t="n">
         <v>0</v>
@@ -64101,13 +64101,13 @@
         <v>1</v>
       </c>
       <c r="Z707" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA707" t="n">
         <v>0</v>
       </c>
       <c r="AB707" t="n">
-        <v>0.552</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="708">
@@ -64125,37 +64125,37 @@
         <v>2019</v>
       </c>
       <c r="D708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E708" t="n">
         <v>1</v>
       </c>
       <c r="F708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G708" t="n">
         <v>1</v>
       </c>
       <c r="H708" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I708" t="n">
         <v>1</v>
       </c>
       <c r="J708" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K708" t="n">
         <v>1</v>
       </c>
       <c r="L708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M708" t="n">
         <v>1</v>
       </c>
       <c r="N708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O708" t="n">
         <v>1</v>
@@ -64176,7 +64176,7 @@
         <v>1</v>
       </c>
       <c r="U708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V708" t="n">
         <v>0</v>
@@ -64188,16 +64188,16 @@
         <v>0</v>
       </c>
       <c r="Y708" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z708" t="n">
         <v>0</v>
       </c>
       <c r="AA708" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB708" t="n">
-        <v>0.5924</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="709">
@@ -64305,13 +64305,13 @@
         <v>2021</v>
       </c>
       <c r="D710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E710" t="n">
         <v>1</v>
       </c>
       <c r="F710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G710" t="n">
         <v>1</v>
@@ -64329,13 +64329,13 @@
         <v>1</v>
       </c>
       <c r="L710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M710" t="n">
         <v>1</v>
       </c>
       <c r="N710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O710" t="n">
         <v>1</v>
@@ -64362,13 +64362,13 @@
         <v>0</v>
       </c>
       <c r="W710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X710" t="n">
         <v>0</v>
       </c>
       <c r="Y710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z710" t="n">
         <v>0</v>
@@ -64377,7 +64377,7 @@
         <v>0</v>
       </c>
       <c r="AB710" t="n">
-        <v>0.6035</v>
+        <v>0.5208</v>
       </c>
     </row>
     <row r="711">
@@ -64623,7 +64623,7 @@
         <v>0</v>
       </c>
       <c r="T713" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U713" t="n">
         <v>0</v>
@@ -76365,13 +76365,13 @@
         <v>2000</v>
       </c>
       <c r="D844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E844" t="n">
         <v>1</v>
       </c>
       <c r="F844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G844" t="n">
         <v>1</v>
@@ -76389,13 +76389,13 @@
         <v>1</v>
       </c>
       <c r="L844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M844" t="n">
         <v>1</v>
       </c>
       <c r="N844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O844" t="n">
         <v>1</v>
@@ -76416,7 +76416,7 @@
         <v>1</v>
       </c>
       <c r="U844" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V844" t="n">
         <v>1</v>
@@ -76434,10 +76434,10 @@
         <v>0</v>
       </c>
       <c r="AA844" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB844" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="845">
@@ -76545,13 +76545,13 @@
         <v>2002</v>
       </c>
       <c r="D846" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E846" t="n">
         <v>1</v>
       </c>
       <c r="F846" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G846" t="n">
         <v>1</v>
@@ -76569,13 +76569,13 @@
         <v>1</v>
       </c>
       <c r="L846" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M846" t="n">
         <v>1</v>
       </c>
       <c r="N846" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O846" t="n">
         <v>1</v>
@@ -76602,7 +76602,7 @@
         <v>0</v>
       </c>
       <c r="W846" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X846" t="n">
         <v>0</v>
@@ -76614,10 +76614,10 @@
         <v>0</v>
       </c>
       <c r="AA846" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB846" t="n">
-        <v>0.6035</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="847">
@@ -76725,13 +76725,13 @@
         <v>2004</v>
       </c>
       <c r="D848" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E848" t="n">
         <v>1</v>
       </c>
       <c r="F848" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G848" t="n">
         <v>1</v>
@@ -76749,13 +76749,13 @@
         <v>1</v>
       </c>
       <c r="L848" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M848" t="n">
         <v>1</v>
       </c>
       <c r="N848" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O848" t="n">
         <v>1</v>
@@ -76779,7 +76779,7 @@
         <v>1</v>
       </c>
       <c r="V848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W848" t="n">
         <v>0</v>
@@ -76794,10 +76794,10 @@
         <v>1</v>
       </c>
       <c r="AA848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB848" t="n">
-        <v>0.6035</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="849">
@@ -78795,40 +78795,40 @@
         <v>1996</v>
       </c>
       <c r="D871" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F871" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H871" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J871" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L871" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N871" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P871" t="n">
         <v>0</v>
@@ -78843,31 +78843,31 @@
         <v>0</v>
       </c>
       <c r="T871" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V871" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X871" t="n">
         <v>0</v>
       </c>
       <c r="Y871" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z871" t="n">
         <v>0</v>
       </c>
       <c r="AA871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB871" t="n">
-        <v>0</v>
+        <v>0.6806</v>
       </c>
     </row>
     <row r="872">
@@ -78975,16 +78975,16 @@
         <v>1998</v>
       </c>
       <c r="D873" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F873" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -78999,16 +78999,16 @@
         <v>0</v>
       </c>
       <c r="L873" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N873" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P873" t="n">
         <v>0</v>
@@ -79023,16 +79023,16 @@
         <v>0</v>
       </c>
       <c r="T873" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U873" t="n">
         <v>0</v>
       </c>
       <c r="V873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X873" t="n">
         <v>0</v>
@@ -79041,13 +79041,13 @@
         <v>0</v>
       </c>
       <c r="Z873" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA873" t="n">
         <v>0</v>
       </c>
       <c r="AB873" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="874">
@@ -79155,40 +79155,40 @@
         <v>2000</v>
       </c>
       <c r="D875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P875" t="n">
         <v>0</v>
@@ -79209,7 +79209,7 @@
         <v>0</v>
       </c>
       <c r="V875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W875" t="n">
         <v>0</v>
@@ -79221,13 +79221,13 @@
         <v>0</v>
       </c>
       <c r="Z875" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA875" t="n">
         <v>0</v>
       </c>
       <c r="AB875" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="876">
@@ -79245,16 +79245,16 @@
         <v>2001</v>
       </c>
       <c r="D876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -79269,16 +79269,16 @@
         <v>0</v>
       </c>
       <c r="L876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P876" t="n">
         <v>0</v>
@@ -79296,7 +79296,7 @@
         <v>0</v>
       </c>
       <c r="U876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V876" t="n">
         <v>0</v>
@@ -79308,7 +79308,7 @@
         <v>0</v>
       </c>
       <c r="Y876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z876" t="n">
         <v>0</v>
@@ -79317,7 +79317,7 @@
         <v>0</v>
       </c>
       <c r="AB876" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="877">
@@ -79335,16 +79335,16 @@
         <v>2002</v>
       </c>
       <c r="D877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -79359,16 +79359,16 @@
         <v>0</v>
       </c>
       <c r="L877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P877" t="n">
         <v>0</v>
@@ -79383,13 +79383,13 @@
         <v>0</v>
       </c>
       <c r="T877" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U877" t="n">
         <v>0</v>
       </c>
       <c r="V877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W877" t="n">
         <v>0</v>
@@ -79401,13 +79401,13 @@
         <v>0</v>
       </c>
       <c r="Z877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA877" t="n">
         <v>0</v>
       </c>
       <c r="AB877" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="878">
@@ -79515,40 +79515,40 @@
         <v>2004</v>
       </c>
       <c r="D879" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F879" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H879" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J879" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L879" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N879" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P879" t="n">
         <v>0</v>
@@ -79563,7 +79563,7 @@
         <v>0</v>
       </c>
       <c r="T879" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U879" t="n">
         <v>0</v>
@@ -79572,22 +79572,22 @@
         <v>0</v>
       </c>
       <c r="W879" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X879" t="n">
         <v>0</v>
       </c>
       <c r="Y879" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA879" t="n">
         <v>0</v>
       </c>
       <c r="AB879" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="880">
@@ -79605,40 +79605,40 @@
         <v>2005</v>
       </c>
       <c r="D880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P880" t="n">
         <v>0</v>
@@ -79662,7 +79662,7 @@
         <v>0</v>
       </c>
       <c r="W880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X880" t="n">
         <v>0</v>
@@ -79674,10 +79674,10 @@
         <v>0</v>
       </c>
       <c r="AA880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB880" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="881">
@@ -79695,40 +79695,40 @@
         <v>2006</v>
       </c>
       <c r="D881" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F881" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H881" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J881" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L881" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N881" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P881" t="n">
         <v>0</v>
@@ -79743,13 +79743,13 @@
         <v>0</v>
       </c>
       <c r="T881" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U881" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W881" t="n">
         <v>0</v>
@@ -79758,16 +79758,16 @@
         <v>0</v>
       </c>
       <c r="Y881" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB881" t="n">
-        <v>0</v>
+        <v>0.6806</v>
       </c>
     </row>
     <row r="882">
@@ -79833,7 +79833,7 @@
         <v>0</v>
       </c>
       <c r="T882" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U882" t="n">
         <v>0</v>
@@ -79875,16 +79875,16 @@
         <v>2008</v>
       </c>
       <c r="D883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -79899,16 +79899,16 @@
         <v>0</v>
       </c>
       <c r="L883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P883" t="n">
         <v>0</v>
@@ -79923,7 +79923,7 @@
         <v>0</v>
       </c>
       <c r="T883" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U883" t="n">
         <v>0</v>
@@ -79932,7 +79932,7 @@
         <v>0</v>
       </c>
       <c r="W883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X883" t="n">
         <v>0</v>
@@ -79944,10 +79944,10 @@
         <v>0</v>
       </c>
       <c r="AA883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB883" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="884">
@@ -79965,40 +79965,40 @@
         <v>2009</v>
       </c>
       <c r="D884" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F884" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L884" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N884" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P884" t="n">
         <v>0</v>
@@ -80019,25 +80019,25 @@
         <v>0</v>
       </c>
       <c r="V884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W884" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X884" t="n">
         <v>0</v>
       </c>
       <c r="Y884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB884" t="n">
-        <v>0</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="885">
@@ -80055,10 +80055,10 @@
         <v>2010</v>
       </c>
       <c r="D885" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E885" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F885" t="n">
         <v>0</v>
@@ -80106,7 +80106,7 @@
         <v>0</v>
       </c>
       <c r="U885" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V885" t="n">
         <v>0</v>
@@ -80127,7 +80127,7 @@
         <v>0</v>
       </c>
       <c r="AB885" t="n">
-        <v>0</v>
+        <v>0.1035</v>
       </c>
     </row>
     <row r="886">
@@ -80145,40 +80145,40 @@
         <v>2011</v>
       </c>
       <c r="D886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P886" t="n">
         <v>0</v>
@@ -80202,13 +80202,13 @@
         <v>0</v>
       </c>
       <c r="W886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X886" t="n">
         <v>0</v>
       </c>
       <c r="Y886" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z886" t="n">
         <v>0</v>
@@ -80217,7 +80217,7 @@
         <v>0</v>
       </c>
       <c r="AB886" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="887">
@@ -80235,40 +80235,40 @@
         <v>2012</v>
       </c>
       <c r="D887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P887" t="n">
         <v>0</v>
@@ -80283,22 +80283,22 @@
         <v>0</v>
       </c>
       <c r="T887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U887" t="n">
         <v>0</v>
       </c>
       <c r="V887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X887" t="n">
         <v>0</v>
       </c>
       <c r="Y887" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z887" t="n">
         <v>0</v>
@@ -80307,7 +80307,7 @@
         <v>0</v>
       </c>
       <c r="AB887" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="888">
@@ -80325,40 +80325,40 @@
         <v>2013</v>
       </c>
       <c r="D888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P888" t="n">
         <v>0</v>
@@ -80373,7 +80373,7 @@
         <v>0</v>
       </c>
       <c r="T888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U888" t="n">
         <v>0</v>
@@ -80382,13 +80382,13 @@
         <v>0</v>
       </c>
       <c r="W888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X888" t="n">
         <v>0</v>
       </c>
       <c r="Y888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z888" t="n">
         <v>0</v>
@@ -80397,7 +80397,7 @@
         <v>0</v>
       </c>
       <c r="AB888" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="889">
@@ -80415,40 +80415,40 @@
         <v>2014</v>
       </c>
       <c r="D889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P889" t="n">
         <v>0</v>
@@ -80463,31 +80463,31 @@
         <v>0</v>
       </c>
       <c r="T889" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V889" t="n">
         <v>0</v>
       </c>
       <c r="W889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X889" t="n">
         <v>0</v>
       </c>
       <c r="Y889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z889" t="n">
         <v>0</v>
       </c>
       <c r="AA889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB889" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="890">
@@ -80505,40 +80505,40 @@
         <v>2015</v>
       </c>
       <c r="D890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P890" t="n">
         <v>0</v>
@@ -80562,13 +80562,13 @@
         <v>0</v>
       </c>
       <c r="W890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X890" t="n">
         <v>0</v>
       </c>
       <c r="Y890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z890" t="n">
         <v>0</v>
@@ -80577,7 +80577,7 @@
         <v>0</v>
       </c>
       <c r="AB890" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="891">
@@ -80595,40 +80595,40 @@
         <v>2016</v>
       </c>
       <c r="D891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P891" t="n">
         <v>0</v>
@@ -80643,7 +80643,7 @@
         <v>0</v>
       </c>
       <c r="T891" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U891" t="n">
         <v>0</v>
@@ -80652,7 +80652,7 @@
         <v>0</v>
       </c>
       <c r="W891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X891" t="n">
         <v>0</v>
@@ -80661,13 +80661,13 @@
         <v>0</v>
       </c>
       <c r="Z891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA891" t="n">
         <v>0</v>
       </c>
       <c r="AB891" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="892">
@@ -80733,7 +80733,7 @@
         <v>0</v>
       </c>
       <c r="T892" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U892" t="n">
         <v>0</v>
@@ -80823,7 +80823,7 @@
         <v>0</v>
       </c>
       <c r="T893" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U893" t="n">
         <v>1</v>
@@ -80913,7 +80913,7 @@
         <v>0</v>
       </c>
       <c r="T894" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U894" t="n">
         <v>0</v>
@@ -81003,7 +81003,7 @@
         <v>0</v>
       </c>
       <c r="T895" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U895" t="n">
         <v>0</v>
@@ -82125,37 +82125,37 @@
         <v>2002</v>
       </c>
       <c r="D908" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E908" t="n">
         <v>1</v>
       </c>
       <c r="F908" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G908" t="n">
         <v>1</v>
       </c>
       <c r="H908" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I908" t="n">
         <v>1</v>
       </c>
       <c r="J908" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K908" t="n">
         <v>1</v>
       </c>
       <c r="L908" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M908" t="n">
         <v>1</v>
       </c>
       <c r="N908" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O908" t="n">
         <v>1</v>
@@ -82176,10 +82176,10 @@
         <v>0</v>
       </c>
       <c r="U908" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V908" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W908" t="n">
         <v>0</v>
@@ -82188,16 +82188,16 @@
         <v>0</v>
       </c>
       <c r="Y908" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z908" t="n">
         <v>0</v>
       </c>
       <c r="AA908" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB908" t="n">
-        <v>0.677</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="909">
@@ -82215,37 +82215,37 @@
         <v>2003</v>
       </c>
       <c r="D909" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E909" t="n">
         <v>1</v>
       </c>
       <c r="F909" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G909" t="n">
         <v>1</v>
       </c>
       <c r="H909" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I909" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J909" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K909" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L909" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M909" t="n">
         <v>1</v>
       </c>
       <c r="N909" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O909" t="n">
         <v>1</v>
@@ -82266,7 +82266,7 @@
         <v>0</v>
       </c>
       <c r="U909" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V909" t="n">
         <v>0</v>
@@ -82278,7 +82278,7 @@
         <v>0</v>
       </c>
       <c r="Y909" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z909" t="n">
         <v>1</v>
@@ -82287,7 +82287,7 @@
         <v>0</v>
       </c>
       <c r="AB909" t="n">
-        <v>0.427</v>
+        <v>0.5404</v>
       </c>
     </row>
     <row r="910">
@@ -82305,16 +82305,16 @@
         <v>2004</v>
       </c>
       <c r="D910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -82329,16 +82329,16 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P910" t="n">
         <v>0</v>
@@ -82356,7 +82356,7 @@
         <v>0</v>
       </c>
       <c r="U910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V910" t="n">
         <v>0</v>
@@ -82377,7 +82377,7 @@
         <v>0</v>
       </c>
       <c r="AB910" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="911">
@@ -82575,40 +82575,40 @@
         <v>2007</v>
       </c>
       <c r="D913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P913" t="n">
         <v>0</v>
@@ -82632,13 +82632,13 @@
         <v>0</v>
       </c>
       <c r="W913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X913" t="n">
         <v>0</v>
       </c>
       <c r="Y913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z913" t="n">
         <v>0</v>
@@ -82647,7 +82647,7 @@
         <v>0</v>
       </c>
       <c r="AB913" t="n">
-        <v>0.6035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="914">
@@ -83745,13 +83745,13 @@
         <v>2020</v>
       </c>
       <c r="D926" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E926" t="n">
         <v>1</v>
       </c>
       <c r="F926" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G926" t="n">
         <v>1</v>
@@ -83769,13 +83769,13 @@
         <v>1</v>
       </c>
       <c r="L926" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M926" t="n">
         <v>1</v>
       </c>
       <c r="N926" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O926" t="n">
         <v>1</v>
@@ -83802,13 +83802,13 @@
         <v>0</v>
       </c>
       <c r="W926" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X926" t="n">
         <v>0</v>
       </c>
       <c r="Y926" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z926" t="n">
         <v>0</v>
@@ -83817,7 +83817,7 @@
         <v>0</v>
       </c>
       <c r="AB926" t="n">
-        <v>0.6035</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="927">
@@ -85377,13 +85377,13 @@
         <v>1</v>
       </c>
       <c r="H944" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I944" t="n">
         <v>1</v>
       </c>
       <c r="J944" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K944" t="n">
         <v>1</v>
@@ -85437,7 +85437,7 @@
         <v>0</v>
       </c>
       <c r="AB944" t="n">
-        <v>0.6806</v>
+        <v>0.6306</v>
       </c>
     </row>
     <row r="945">
@@ -85455,16 +85455,16 @@
         <v>2008</v>
       </c>
       <c r="D945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -85479,16 +85479,16 @@
         <v>0</v>
       </c>
       <c r="L945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P945" t="n">
         <v>0</v>
@@ -85512,7 +85512,7 @@
         <v>0</v>
       </c>
       <c r="W945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X945" t="n">
         <v>0</v>
@@ -85524,10 +85524,10 @@
         <v>0</v>
       </c>
       <c r="AA945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB945" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="946">
@@ -85545,16 +85545,16 @@
         <v>2009</v>
       </c>
       <c r="D946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -85569,16 +85569,16 @@
         <v>0</v>
       </c>
       <c r="L946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P946" t="n">
         <v>0</v>
@@ -85599,7 +85599,7 @@
         <v>0</v>
       </c>
       <c r="V946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W946" t="n">
         <v>0</v>
@@ -85608,7 +85608,7 @@
         <v>0</v>
       </c>
       <c r="Y946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z946" t="n">
         <v>0</v>
@@ -85617,7 +85617,7 @@
         <v>0</v>
       </c>
       <c r="AB946" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="947">
@@ -85635,37 +85635,37 @@
         <v>2010</v>
       </c>
       <c r="D947" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E947" t="n">
         <v>1</v>
       </c>
       <c r="F947" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G947" t="n">
         <v>1</v>
       </c>
       <c r="H947" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I947" t="n">
         <v>1</v>
       </c>
       <c r="J947" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K947" t="n">
         <v>1</v>
       </c>
       <c r="L947" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M947" t="n">
         <v>1</v>
       </c>
       <c r="N947" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O947" t="n">
         <v>1</v>
@@ -85689,7 +85689,7 @@
         <v>2</v>
       </c>
       <c r="V947" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W947" t="n">
         <v>0</v>
@@ -85698,7 +85698,7 @@
         <v>0</v>
       </c>
       <c r="Y947" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z947" t="n">
         <v>0</v>
@@ -85707,7 +85707,7 @@
         <v>1</v>
       </c>
       <c r="AB947" t="n">
-        <v>0.6549</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="948">
@@ -85905,37 +85905,37 @@
         <v>2013</v>
       </c>
       <c r="D950" t="n">
+        <v>5</v>
+      </c>
+      <c r="E950" t="n">
+        <v>1</v>
+      </c>
+      <c r="F950" t="n">
+        <v>5</v>
+      </c>
+      <c r="G950" t="n">
+        <v>1</v>
+      </c>
+      <c r="H950" t="n">
         <v>3</v>
       </c>
-      <c r="E950" t="n">
-        <v>1</v>
-      </c>
-      <c r="F950" t="n">
+      <c r="I950" t="n">
+        <v>1</v>
+      </c>
+      <c r="J950" t="n">
         <v>3</v>
       </c>
-      <c r="G950" t="n">
-        <v>1</v>
-      </c>
-      <c r="H950" t="n">
-        <v>1</v>
-      </c>
-      <c r="I950" t="n">
-        <v>1</v>
-      </c>
-      <c r="J950" t="n">
-        <v>1</v>
-      </c>
       <c r="K950" t="n">
         <v>1</v>
       </c>
       <c r="L950" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M950" t="n">
         <v>1</v>
       </c>
       <c r="N950" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O950" t="n">
         <v>1</v>
@@ -85956,19 +85956,19 @@
         <v>5</v>
       </c>
       <c r="U950" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V950" t="n">
         <v>1</v>
       </c>
       <c r="W950" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X950" t="n">
         <v>0</v>
       </c>
       <c r="Y950" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z950" t="n">
         <v>2</v>
@@ -85977,7 +85977,7 @@
         <v>0</v>
       </c>
       <c r="AB950" t="n">
-        <v>0.5716</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="951">
@@ -87579,10 +87579,10 @@
         <v>1</v>
       </c>
       <c r="V968" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W968" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X968" t="n">
         <v>0</v>
@@ -87591,7 +87591,7 @@
         <v>1</v>
       </c>
       <c r="Z968" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA968" t="n">
         <v>0</v>
@@ -87615,40 +87615,40 @@
         <v>2001</v>
       </c>
       <c r="D969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P969" t="n">
         <v>0</v>
@@ -87666,7 +87666,7 @@
         <v>1</v>
       </c>
       <c r="U969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V969" t="n">
         <v>0</v>
@@ -87678,7 +87678,7 @@
         <v>0</v>
       </c>
       <c r="Y969" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z969" t="n">
         <v>0</v>
@@ -87687,7 +87687,7 @@
         <v>0</v>
       </c>
       <c r="AB969" t="n">
-        <v>0.6035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="970">
@@ -87705,37 +87705,37 @@
         <v>2002</v>
       </c>
       <c r="D970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E970" t="n">
         <v>1</v>
       </c>
       <c r="F970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G970" t="n">
         <v>1</v>
       </c>
       <c r="H970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I970" t="n">
         <v>1</v>
       </c>
       <c r="J970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K970" t="n">
         <v>1</v>
       </c>
       <c r="L970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M970" t="n">
         <v>1</v>
       </c>
       <c r="N970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O970" t="n">
         <v>1</v>
@@ -87762,7 +87762,7 @@
         <v>0</v>
       </c>
       <c r="W970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X970" t="n">
         <v>0</v>
@@ -87774,10 +87774,10 @@
         <v>0</v>
       </c>
       <c r="AA970" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB970" t="n">
-        <v>0.6035</v>
+        <v>0.6458</v>
       </c>
     </row>
     <row r="971">
@@ -89865,37 +89865,37 @@
         <v>1995</v>
       </c>
       <c r="D994" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E994" t="n">
         <v>1</v>
       </c>
       <c r="F994" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G994" t="n">
         <v>1</v>
       </c>
       <c r="H994" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I994" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J994" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K994" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L994" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M994" t="n">
         <v>1</v>
       </c>
       <c r="N994" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O994" t="n">
         <v>1</v>
@@ -89916,7 +89916,7 @@
         <v>0</v>
       </c>
       <c r="U994" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V994" t="n">
         <v>1</v>
@@ -89937,7 +89937,7 @@
         <v>1</v>
       </c>
       <c r="AB994" t="n">
-        <v>0.3535</v>
+        <v>0.6458</v>
       </c>
     </row>
     <row r="995">
@@ -90045,16 +90045,16 @@
         <v>1997</v>
       </c>
       <c r="D996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -90069,16 +90069,16 @@
         <v>0</v>
       </c>
       <c r="L996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P996" t="n">
         <v>0</v>
@@ -90099,7 +90099,7 @@
         <v>0</v>
       </c>
       <c r="V996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W996" t="n">
         <v>0</v>
@@ -90114,10 +90114,10 @@
         <v>0</v>
       </c>
       <c r="AA996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB996" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="997">
@@ -90183,7 +90183,7 @@
         <v>0</v>
       </c>
       <c r="T997" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U997" t="n">
         <v>1</v>
@@ -90225,13 +90225,13 @@
         <v>1999</v>
       </c>
       <c r="D998" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E998" t="n">
         <v>1</v>
       </c>
       <c r="F998" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G998" t="n">
         <v>1</v>
@@ -90249,13 +90249,13 @@
         <v>0</v>
       </c>
       <c r="L998" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M998" t="n">
         <v>1</v>
       </c>
       <c r="N998" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O998" t="n">
         <v>1</v>
@@ -90282,13 +90282,13 @@
         <v>1</v>
       </c>
       <c r="W998" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X998" t="n">
         <v>0</v>
       </c>
       <c r="Y998" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z998" t="n">
         <v>0</v>
@@ -90297,7 +90297,7 @@
         <v>0</v>
       </c>
       <c r="AB998" t="n">
-        <v>0.3535</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="999">
@@ -90315,13 +90315,13 @@
         <v>2000</v>
       </c>
       <c r="D999" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E999" t="n">
         <v>1</v>
       </c>
       <c r="F999" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G999" t="n">
         <v>1</v>
@@ -90339,13 +90339,13 @@
         <v>1</v>
       </c>
       <c r="L999" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M999" t="n">
         <v>1</v>
       </c>
       <c r="N999" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O999" t="n">
         <v>1</v>
@@ -90366,7 +90366,7 @@
         <v>0</v>
       </c>
       <c r="U999" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V999" t="n">
         <v>0</v>
@@ -90378,7 +90378,7 @@
         <v>0</v>
       </c>
       <c r="Y999" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z999" t="n">
         <v>0</v>
@@ -90387,7 +90387,7 @@
         <v>0</v>
       </c>
       <c r="AB999" t="n">
-        <v>0.6035</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="1000">
@@ -90405,40 +90405,40 @@
         <v>2001</v>
       </c>
       <c r="D1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1000" t="n">
         <v>0</v>
@@ -90456,10 +90456,10 @@
         <v>0</v>
       </c>
       <c r="U1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1000" t="n">
         <v>0</v>
@@ -90468,7 +90468,7 @@
         <v>0</v>
       </c>
       <c r="Y1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z1000" t="n">
         <v>0</v>
@@ -90477,7 +90477,7 @@
         <v>0</v>
       </c>
       <c r="AB1000" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="1001">
@@ -90495,40 +90495,40 @@
         <v>2002</v>
       </c>
       <c r="D1001" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1001" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1001" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1001" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1001" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1001" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1001" t="n">
         <v>0</v>
@@ -90546,28 +90546,28 @@
         <v>0</v>
       </c>
       <c r="U1001" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V1001" t="n">
         <v>0</v>
       </c>
       <c r="W1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y1001" t="n">
         <v>0</v>
       </c>
       <c r="Z1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA1001" t="n">
         <v>0</v>
       </c>
       <c r="AB1001" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="1002">
@@ -90585,13 +90585,13 @@
         <v>2003</v>
       </c>
       <c r="D1002" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1002" t="n">
         <v>1</v>
       </c>
       <c r="F1002" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1002" t="n">
         <v>1</v>
@@ -90609,13 +90609,13 @@
         <v>0</v>
       </c>
       <c r="L1002" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M1002" t="n">
         <v>1</v>
       </c>
       <c r="N1002" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O1002" t="n">
         <v>1</v>
@@ -90639,7 +90639,7 @@
         <v>0</v>
       </c>
       <c r="V1002" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1002" t="n">
         <v>1</v>
@@ -90654,10 +90654,10 @@
         <v>0</v>
       </c>
       <c r="AA1002" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1002" t="n">
-        <v>0.3535</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="1003">
@@ -90675,40 +90675,40 @@
         <v>2004</v>
       </c>
       <c r="D1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1003" t="n">
         <v>0</v>
@@ -90723,31 +90723,31 @@
         <v>0</v>
       </c>
       <c r="T1003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1003" t="n">
         <v>0</v>
       </c>
       <c r="V1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1003" t="n">
         <v>0</v>
       </c>
       <c r="Y1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA1003" t="n">
         <v>0</v>
       </c>
       <c r="AB1003" t="n">
-        <v>0</v>
+        <v>0.6458</v>
       </c>
     </row>
     <row r="1004">
@@ -90765,40 +90765,40 @@
         <v>2005</v>
       </c>
       <c r="D1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1004" t="n">
         <v>0</v>
@@ -90816,10 +90816,10 @@
         <v>0</v>
       </c>
       <c r="U1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1004" t="n">
         <v>0</v>
@@ -90828,7 +90828,7 @@
         <v>0</v>
       </c>
       <c r="Y1004" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1004" t="n">
         <v>0</v>
@@ -90837,7 +90837,7 @@
         <v>0</v>
       </c>
       <c r="AB1004" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="1005">
@@ -90855,37 +90855,37 @@
         <v>2006</v>
       </c>
       <c r="D1005" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1005" t="n">
         <v>1</v>
       </c>
       <c r="F1005" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1005" t="n">
         <v>1</v>
       </c>
       <c r="H1005" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I1005" t="n">
         <v>1</v>
       </c>
       <c r="J1005" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1005" t="n">
         <v>1</v>
       </c>
       <c r="L1005" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M1005" t="n">
         <v>1</v>
       </c>
       <c r="N1005" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O1005" t="n">
         <v>1</v>
@@ -90903,31 +90903,31 @@
         <v>0</v>
       </c>
       <c r="T1005" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U1005" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V1005" t="n">
         <v>0</v>
       </c>
       <c r="W1005" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1005" t="n">
         <v>0</v>
       </c>
       <c r="Y1005" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z1005" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA1005" t="n">
         <v>0</v>
       </c>
       <c r="AB1005" t="n">
-        <v>0.6035</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="1006">
@@ -91035,40 +91035,40 @@
         <v>2008</v>
       </c>
       <c r="D1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1007" t="n">
         <v>0</v>
@@ -91086,7 +91086,7 @@
         <v>0</v>
       </c>
       <c r="U1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1007" t="n">
         <v>0</v>
@@ -91098,7 +91098,7 @@
         <v>0</v>
       </c>
       <c r="Y1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1007" t="n">
         <v>0</v>
@@ -91107,7 +91107,7 @@
         <v>0</v>
       </c>
       <c r="AB1007" t="n">
-        <v>0</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="1008">
@@ -91215,16 +91215,16 @@
         <v>2010</v>
       </c>
       <c r="D1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -91239,16 +91239,16 @@
         <v>0</v>
       </c>
       <c r="L1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1009" t="n">
         <v>0</v>
@@ -91263,7 +91263,7 @@
         <v>0</v>
       </c>
       <c r="T1009" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1009" t="n">
         <v>0</v>
@@ -91272,13 +91272,13 @@
         <v>0</v>
       </c>
       <c r="W1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1009" t="n">
         <v>0</v>
       </c>
       <c r="Y1009" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1009" t="n">
         <v>0</v>
@@ -91287,7 +91287,7 @@
         <v>0</v>
       </c>
       <c r="AB1009" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="1010">
@@ -91443,7 +91443,7 @@
         <v>0</v>
       </c>
       <c r="T1011" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U1011" t="n">
         <v>0</v>
@@ -91575,40 +91575,40 @@
         <v>2014</v>
       </c>
       <c r="D1013" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1013" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1013" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1013" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1013" t="n">
         <v>0</v>
@@ -91623,31 +91623,31 @@
         <v>0</v>
       </c>
       <c r="T1013" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U1013" t="n">
         <v>0</v>
       </c>
       <c r="V1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1013" t="n">
         <v>0</v>
       </c>
       <c r="Y1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1013" t="n">
         <v>0</v>
       </c>
       <c r="AA1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1013" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="1014">
@@ -91677,16 +91677,16 @@
         <v>1</v>
       </c>
       <c r="H1014" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1014" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1014" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1014" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1014" t="n">
         <v>1</v>
@@ -91737,7 +91737,7 @@
         <v>0</v>
       </c>
       <c r="AB1014" t="n">
-        <v>0.6035</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="1015">
@@ -91845,37 +91845,37 @@
         <v>2017</v>
       </c>
       <c r="D1016" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1016" t="n">
         <v>1</v>
       </c>
       <c r="F1016" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1016" t="n">
         <v>1</v>
       </c>
       <c r="H1016" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1016" t="n">
         <v>1</v>
       </c>
       <c r="J1016" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1016" t="n">
         <v>1</v>
       </c>
       <c r="L1016" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M1016" t="n">
         <v>1</v>
       </c>
       <c r="N1016" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O1016" t="n">
         <v>1</v>
@@ -91896,28 +91896,28 @@
         <v>4</v>
       </c>
       <c r="U1016" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V1016" t="n">
         <v>1</v>
       </c>
       <c r="W1016" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X1016" t="n">
         <v>0</v>
       </c>
       <c r="Y1016" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1016" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA1016" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB1016" t="n">
-        <v>0.6306</v>
+        <v>0.6978</v>
       </c>
     </row>
     <row r="1017">
